--- a/source_data/Figure3.xlsx
+++ b/source_data/Figure3.xlsx
@@ -5,15 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weikangshi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weikangshi/Desktop/PostDoc/manuscripts_move_to_dropbox/gaze_accumulation_marmoset_dmPFC/final_after_rebuttal/source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{144DA8A5-72E6-904B-AF30-4E6141D76A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99221748-BF9E-8745-800B-1B8F89CA2F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="5480" windowWidth="28040" windowHeight="17180" xr2:uid="{CDD6E5A6-FA5B-EC4D-9D0B-223207B8A016}"/>
+    <workbookView xWindow="4780" yWindow="1000" windowWidth="33200" windowHeight="26940" activeTab="2" xr2:uid="{CDD6E5A6-FA5B-EC4D-9D0B-223207B8A016}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="panelA" sheetId="2" r:id="rId1"/>
+    <sheet name="panelB" sheetId="3" r:id="rId2"/>
+    <sheet name="panelE" sheetId="1" r:id="rId3"/>
+    <sheet name="panelF" sheetId="4" r:id="rId4"/>
+    <sheet name="panelG" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,12 +39,54 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+  <si>
+    <t>correlation coeffient</t>
+  </si>
+  <si>
+    <t>Animal K</t>
+  </si>
+  <si>
+    <t>Animal D</t>
+  </si>
+  <si>
+    <t>coefficient value</t>
+  </si>
+  <si>
+    <t>animal K</t>
+  </si>
+  <si>
+    <t>animal D</t>
+  </si>
+  <si>
+    <t>beta 1</t>
+  </si>
+  <si>
+    <t>beta 2</t>
+  </si>
+  <si>
+    <t>coefficient value beta z</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.000000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,8 +112,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,10 +457,6160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584E4DF8-6FF4-584C-AD7F-D532BD7F03CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F466F093-1B58-5146-BE59-A52BC4F8AE9C}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AE5155-D8FE-474D-9332-E45648E3C309}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584E4DF8-6FF4-584C-AD7F-D532BD7F03CF}">
+  <dimension ref="A1:D467"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>0.38994877781680898</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.110750938775457</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.31994298467829801</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2.5627854764715199E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>0.33925533877386199</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.152150174125498</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.34146689267660602</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-2.80627242526677E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>0.40925888242610797</v>
+      </c>
+      <c r="B6">
+        <v>-5.99913872985295E-2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.37480174432480001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3.5515210173819901E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>0.81824735884802002</v>
+      </c>
+      <c r="B7">
+        <v>4.2269708695130602E-2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.46181277639517898</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.00618430766546E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>0.58914424944928001</v>
+      </c>
+      <c r="B8">
+        <v>-9.7442393391640701E-3</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-2.52158E-2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>-1.07821761973607E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>0.78597337225022301</v>
+      </c>
+      <c r="B9">
+        <v>7.8740232133025098E-2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.43145658851797403</v>
+      </c>
+      <c r="D9" s="4">
+        <v>-0.11970785304482701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>0.43204165988048099</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.125089119072187</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.40655403694044201</v>
+      </c>
+      <c r="D10" s="4">
+        <v>-2.3529278940201299E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>0.519266475886067</v>
+      </c>
+      <c r="B11">
+        <v>-0.121660794880776</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.38351492104547602</v>
+      </c>
+      <c r="D11" s="4">
+        <v>-3.4790315843075098E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>0.26480311781737398</v>
+      </c>
+      <c r="B12">
+        <v>-1.30956560215681E-2</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.39095329446904398</v>
+      </c>
+      <c r="D12" s="4">
+        <v>8.6170614265269604E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>0.41277630763547002</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.102434370610427</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.48204799303389301</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.104442912726167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>0.80071684619412298</v>
+      </c>
+      <c r="B14">
+        <v>8.0079782327901805E-2</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0.30582819642203701</v>
+      </c>
+      <c r="D14" s="4">
+        <v>6.8393874796535595E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>0.35386310114585701</v>
+      </c>
+      <c r="B15">
+        <v>5.78117405491844E-2</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.42215584389926603</v>
+      </c>
+      <c r="D15" s="6">
+        <v>5.2738261337554902E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>0.46787342779491098</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.48322186281951E-2</v>
+      </c>
+      <c r="C16" s="5">
+        <v>9.8889420000000006E-2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5.1441048743425895E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>0.33023792999895701</v>
+      </c>
+      <c r="B17">
+        <v>-4.3194086758701303E-2</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.154065079284224</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.120140961212873</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>0.23284269062544599</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5.0349416656796001E-2</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.52458754728143497</v>
+      </c>
+      <c r="D18" s="4">
+        <v>9.8361950048842905E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>0.228682315432616</v>
+      </c>
+      <c r="B19">
+        <v>-6.5951647276414893E-2</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.49851263710419802</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2.53893562355018E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>0.732272978992344</v>
+      </c>
+      <c r="B20">
+        <v>7.6193519907853599E-2</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.73325109023766699</v>
+      </c>
+      <c r="D20" s="4">
+        <v>7.0324923877839304E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>0.18555714295279899</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2.8205024864281301E-2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.21383744078153499</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.10647613724854001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0.73241258706225099</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.13802231519226599</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1.1822311033461601</v>
+      </c>
+      <c r="D22" s="4">
+        <v>-3.9324405536885397E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>0.43042717557433702</v>
+      </c>
+      <c r="B23">
+        <v>-5.5325651474448403E-4</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.70125949758955997</v>
+      </c>
+      <c r="D23" s="4">
+        <v>-9.1474458429333994E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>0.23181388511851</v>
+      </c>
+      <c r="B24">
+        <v>-5.9009598901834999E-2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.68473214072757105</v>
+      </c>
+      <c r="D24" s="6">
+        <v>4.4650359847448098E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>0.45090341486163499</v>
+      </c>
+      <c r="B25">
+        <v>-2.07399467828304E-2</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0.36560155378774101</v>
+      </c>
+      <c r="D25" s="6">
+        <v>5.4045554418663697E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>0.410246217504456</v>
+      </c>
+      <c r="B26">
+        <v>8.8171627838822004E-3</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0.27061326631171401</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3.3761443119438801E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>0.31910987657641099</v>
+      </c>
+      <c r="B27">
+        <v>3.5165912968473503E-2</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.168134742032228</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2.7101975695529398E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>8.3513907769613704E-2</v>
+      </c>
+      <c r="B28" s="2">
+        <v>5.6262699707243E-2</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.61148378699121297</v>
+      </c>
+      <c r="D28" s="4">
+        <v>-7.3942064047448797E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>0.220866168779599</v>
+      </c>
+      <c r="B29">
+        <v>-7.9947915760498006E-2</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.61018013999999998</v>
+      </c>
+      <c r="D29" s="4">
+        <v>-3.9927274509494799E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>0.32466748280977398</v>
+      </c>
+      <c r="B30" s="2">
+        <v>5.7913482094100299E-2</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.18579648152780001</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3.0499612157432899E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>0.39985555179386501</v>
+      </c>
+      <c r="B31">
+        <v>9.1673081528367895E-2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0.52604690915686603</v>
+      </c>
+      <c r="D31" s="4">
+        <v>4.5871572304344702E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>0.58897675254544901</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.105331338669333</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0.85525958318869</v>
+      </c>
+      <c r="D32" s="4">
+        <v>8.4489156665147794E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>0.28309651885049197</v>
+      </c>
+      <c r="B33">
+        <v>2.1405060043380501E-2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0.673637922850021</v>
+      </c>
+      <c r="D33" s="4">
+        <v>-1.50205762489276E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>0.472267191606419</v>
+      </c>
+      <c r="B34">
+        <v>5.1752626178789098E-2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0.89517543113018605</v>
+      </c>
+      <c r="D34" s="4">
+        <v>-5.7026414705347299E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>0.49065512206786499</v>
+      </c>
+      <c r="B35">
+        <v>6.8813669147014894E-2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>0.44246906083755</v>
+      </c>
+      <c r="D35" s="4">
+        <v>8.8065596475898397E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>0.17787198859811601</v>
+      </c>
+      <c r="B36">
+        <v>-6.1664184701245702E-3</v>
+      </c>
+      <c r="C36" s="5">
+        <v>0.46821429761060801</v>
+      </c>
+      <c r="D36" s="4">
+        <v>7.0351151152866401E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>0.20904291828625901</v>
+      </c>
+      <c r="B37">
+        <v>7.6222459805909706E-2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>0.71854464239483595</v>
+      </c>
+      <c r="D37" s="4">
+        <v>-1.7977341126232901E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>0.35102807206117698</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.12077914328431801</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1.0272868771602599</v>
+      </c>
+      <c r="D38" s="4">
+        <v>-9.9615116187595394E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>0.14640167832026199</v>
+      </c>
+      <c r="B39">
+        <v>4.0541592980844199E-2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>0.22129659422551701</v>
+      </c>
+      <c r="D39" s="4">
+        <v>6.70535632224233E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>0.30759298151984399</v>
+      </c>
+      <c r="B40">
+        <v>7.3203711227185206E-2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>0.52585403396556496</v>
+      </c>
+      <c r="D40" s="4">
+        <v>-1.6768087425065002E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>0.217071276584305</v>
+      </c>
+      <c r="B41">
+        <v>1.39031977467337E-2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>0.44237228446415799</v>
+      </c>
+      <c r="D41" s="4">
+        <v>-2.9439198628921699E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>0.25304947145791401</v>
+      </c>
+      <c r="B42">
+        <v>-6.3151436654833498E-2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>0.50809564699120702</v>
+      </c>
+      <c r="D42" s="4">
+        <v>3.76440302927184E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>9.1071111551164693E-2</v>
+      </c>
+      <c r="B43">
+        <v>-4.83196246240657E-2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>0.55995114191125905</v>
+      </c>
+      <c r="D43" s="4">
+        <v>-3.4024224322024503E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>0.50192652534630899</v>
+      </c>
+      <c r="B44">
+        <v>-6.3976020342088699E-2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>0.40646498705186501</v>
+      </c>
+      <c r="D44" s="4">
+        <v>3.9916800577112797E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>0.46890905833528701</v>
+      </c>
+      <c r="B45">
+        <v>6.6850557505560904E-2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>0.39348992743231198</v>
+      </c>
+      <c r="D45" s="4">
+        <v>7.1432229192621405E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>0.52476854865921196</v>
+      </c>
+      <c r="B46">
+        <v>-7.9635181717511605E-2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>0.40509841775311001</v>
+      </c>
+      <c r="D46" s="4">
+        <v>-2.66145677849969E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>0.570469675465615</v>
+      </c>
+      <c r="B47">
+        <v>-0.128127279383218</v>
+      </c>
+      <c r="C47" s="5">
+        <v>0.44032908999999998</v>
+      </c>
+      <c r="D47" s="4">
+        <v>3.9791064474879997E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>0.62603317970972905</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.13096324480410801</v>
+      </c>
+      <c r="C48" s="5">
+        <v>0.41416117449871898</v>
+      </c>
+      <c r="D48" s="6">
+        <v>5.6975323935943997E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>0.52247159498772799</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.146732832282334</v>
+      </c>
+      <c r="C49" s="5">
+        <v>0.38624381544719399</v>
+      </c>
+      <c r="D49" s="4">
+        <v>-5.2168184207454997E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>0.97827229591377596</v>
+      </c>
+      <c r="B50" s="2">
+        <v>3.1094643182143201E-2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>0.42183599099755198</v>
+      </c>
+      <c r="D50" s="4">
+        <v>7.0499031567887302E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>0.62579270010971999</v>
+      </c>
+      <c r="B51">
+        <v>9.1224754603892094E-2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>0.23066423440755501</v>
+      </c>
+      <c r="D51" s="4">
+        <v>-3.18763326828694E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>0.92546828348384802</v>
+      </c>
+      <c r="B52">
+        <v>-4.6438100240657797E-3</v>
+      </c>
+      <c r="C52" s="5">
+        <v>0.97879565000000002</v>
+      </c>
+      <c r="D52" s="4">
+        <v>-9.3961129990747308E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>0.64821323389641095</v>
+      </c>
+      <c r="B53">
+        <v>-2.6954991485929801E-2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>0.51180559049287</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2.5325125962406301E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>0.33539250283856797</v>
+      </c>
+      <c r="B54">
+        <v>7.3147529983704301E-2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>0.867277190235474</v>
+      </c>
+      <c r="D54" s="4">
+        <v>-4.6592482360787899E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>0.74346895412798697</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.14876675160978101</v>
+      </c>
+      <c r="C55" s="5">
+        <v>0.44700461299383398</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2.0335990626096902E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>0.48366897566358302</v>
+      </c>
+      <c r="B56">
+        <v>7.5186637266351594E-2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>0.237249749097834</v>
+      </c>
+      <c r="D56" s="4">
+        <v>-5.4459387003974499E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>0.448110382769911</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.13466133225291599</v>
+      </c>
+      <c r="C57" s="5">
+        <v>0.61357444341804201</v>
+      </c>
+      <c r="D57" s="4">
+        <v>-2.4337172879582401E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>0.784241766836696</v>
+      </c>
+      <c r="B58">
+        <v>9.4663334375150898E-2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>0.43994962514697999</v>
+      </c>
+      <c r="D58" s="4">
+        <v>6.9137532133602103E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>0.62812122319803698</v>
+      </c>
+      <c r="B59">
+        <v>-9.7084941362886503E-3</v>
+      </c>
+      <c r="C59" s="5">
+        <v>0.47767768387358001</v>
+      </c>
+      <c r="D59" s="4">
+        <v>7.1699379999503293E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>0.59754473846350398</v>
+      </c>
+      <c r="B60">
+        <v>7.6002265250730297E-2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>0.65233502732543402</v>
+      </c>
+      <c r="D60" s="4">
+        <v>6.2733633517479598E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>0.71972805793163597</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.112046781624072</v>
+      </c>
+      <c r="C61" s="5">
+        <v>0.71354730440860004</v>
+      </c>
+      <c r="D61" s="4">
+        <v>-1.45878712777784E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>0.513187266122479</v>
+      </c>
+      <c r="B62">
+        <v>5.6804979802866001E-2</v>
+      </c>
+      <c r="C62" s="5">
+        <v>0.73801250385297001</v>
+      </c>
+      <c r="D62" s="4">
+        <v>2.1507825081763701E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>0.70380368109803304</v>
+      </c>
+      <c r="B63">
+        <v>7.6486348820191105E-2</v>
+      </c>
+      <c r="C63" s="5">
+        <v>0.47226659229020901</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0.10555142764580799</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>0.67823753201331805</v>
+      </c>
+      <c r="B64">
+        <v>7.9262142104517097E-2</v>
+      </c>
+      <c r="C64" s="5">
+        <v>6.8183649999999998E-2</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1.6895653762755199E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>0.58001185588380899</v>
+      </c>
+      <c r="B65" s="2">
+        <v>3.4767010720431799E-2</v>
+      </c>
+      <c r="C65" s="5">
+        <v>0.38186944175572302</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0.119546758661182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>0.58017778811128096</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.106003663414888</v>
+      </c>
+      <c r="C66" s="5">
+        <v>0.18265977256173299</v>
+      </c>
+      <c r="D66" s="4">
+        <v>5.5849944290963002E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>0.56976452425504598</v>
+      </c>
+      <c r="B67">
+        <v>9.5552012774561101E-2</v>
+      </c>
+      <c r="C67" s="5">
+        <v>0.51303836639358702</v>
+      </c>
+      <c r="D67" s="4">
+        <v>7.6167362257783797E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>0.68165641773038999</v>
+      </c>
+      <c r="B68" s="2">
+        <v>5.0546386609604602E-2</v>
+      </c>
+      <c r="C68" s="5">
+        <v>0.423644790576366</v>
+      </c>
+      <c r="D68" s="4">
+        <v>3.7112546745292997E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>0.34376619966334998</v>
+      </c>
+      <c r="B69" s="2">
+        <v>4.8275360856407698E-2</v>
+      </c>
+      <c r="C69" s="5">
+        <v>0.59535300329539997</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0.13039697528406499</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>0.72504673529706398</v>
+      </c>
+      <c r="B70">
+        <v>-7.8599332491655793E-2</v>
+      </c>
+      <c r="C70" s="5">
+        <v>0.47264264469894901</v>
+      </c>
+      <c r="D70" s="4">
+        <v>-1.6771578501302599E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>0.92748567448822095</v>
+      </c>
+      <c r="B71">
+        <v>8.3868009464249896E-2</v>
+      </c>
+      <c r="C71" s="5">
+        <v>6.5106960000000005E-2</v>
+      </c>
+      <c r="D71" s="4">
+        <v>4.5386649620144303E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>0.71760473033390204</v>
+      </c>
+      <c r="B72">
+        <v>7.6411731131425395E-2</v>
+      </c>
+      <c r="C72" s="5">
+        <v>0.43545084825757502</v>
+      </c>
+      <c r="D72" s="4">
+        <v>-0.100657049147809</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>0.17109419783725299</v>
+      </c>
+      <c r="B73">
+        <v>8.7264746374254798E-2</v>
+      </c>
+      <c r="C73" s="5">
+        <v>0.30715796225171599</v>
+      </c>
+      <c r="D73" s="4">
+        <v>-7.3624503128144905E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>0.392460731031402</v>
+      </c>
+      <c r="B74">
+        <v>7.6056606553752099E-2</v>
+      </c>
+      <c r="C74" s="5">
+        <v>0.47926455667911999</v>
+      </c>
+      <c r="D74" s="4">
+        <v>-6.5893445846107804E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>0.474845948880665</v>
+      </c>
+      <c r="B75">
+        <v>6.1767770436200201E-2</v>
+      </c>
+      <c r="C75" s="5">
+        <v>0.228504791425508</v>
+      </c>
+      <c r="D75" s="4">
+        <v>2.03266680329714E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>0.33927672639055001</v>
+      </c>
+      <c r="B76" s="2">
+        <v>1.9429553636355699E-2</v>
+      </c>
+      <c r="C76" s="5">
+        <v>1.33727265530565</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1.49770523724463E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>0.72619953165872897</v>
+      </c>
+      <c r="B77">
+        <v>-3.5001778676670398E-2</v>
+      </c>
+      <c r="C77" s="5">
+        <v>0.88179769627695004</v>
+      </c>
+      <c r="D77" s="6">
+        <v>5.8153747458265598E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>7.2996990917798404E-2</v>
+      </c>
+      <c r="B78">
+        <v>6.6524452442368903E-2</v>
+      </c>
+      <c r="C78" s="5">
+        <v>0.36942163972057801</v>
+      </c>
+      <c r="D78" s="4">
+        <v>7.7492110271294601E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>0.36398625164689102</v>
+      </c>
+      <c r="B79">
+        <v>4.0081313198479698E-2</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0.33219452908275099</v>
+      </c>
+      <c r="D79" s="6">
+        <v>0.12456521511758301</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>0.35761960330700798</v>
+      </c>
+      <c r="B80">
+        <v>-2.6613117130486899E-3</v>
+      </c>
+      <c r="C80" s="5">
+        <v>0.6017422</v>
+      </c>
+      <c r="D80" s="4">
+        <v>-0.113116444553042</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>0.319121947681961</v>
+      </c>
+      <c r="B81">
+        <v>5.2215832289942199E-2</v>
+      </c>
+      <c r="C81" s="5">
+        <v>0.59118338217692601</v>
+      </c>
+      <c r="D81" s="4">
+        <v>-3.5511418870963797E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>0.152122622670784</v>
+      </c>
+      <c r="B82">
+        <v>5.0913199467965499E-2</v>
+      </c>
+      <c r="C82" s="5">
+        <v>0.53441946519516303</v>
+      </c>
+      <c r="D82" s="4">
+        <v>2.7878723622310801E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>0.32517810191915197</v>
+      </c>
+      <c r="B83" s="2">
+        <v>0.11063409440946501</v>
+      </c>
+      <c r="C83" s="5">
+        <v>0.156055198355561</v>
+      </c>
+      <c r="D83" s="6">
+        <v>2.4017393284058601E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>0.363278188779115</v>
+      </c>
+      <c r="B84">
+        <v>3.72147426826826E-2</v>
+      </c>
+      <c r="C84" s="5">
+        <v>0.18437744374571099</v>
+      </c>
+      <c r="D84" s="4">
+        <v>-1.99219170455903E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>0.23925835701554399</v>
+      </c>
+      <c r="B85">
+        <v>3.1539204113124599E-3</v>
+      </c>
+      <c r="C85" s="5">
+        <v>0.82592440081308005</v>
+      </c>
+      <c r="D85" s="4">
+        <v>5.13826104109181E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>0.22789673206588901</v>
+      </c>
+      <c r="B86" s="2">
+        <v>2.69427523748938E-2</v>
+      </c>
+      <c r="C86" s="5">
+        <v>1.1986368446578399</v>
+      </c>
+      <c r="D86" s="4">
+        <v>-7.1885636975395906E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>0.13912136479545101</v>
+      </c>
+      <c r="B87" s="2">
+        <v>1.29991770688976E-2</v>
+      </c>
+      <c r="C87" s="5">
+        <v>0.86994404431498096</v>
+      </c>
+      <c r="D87" s="4">
+        <v>5.07043709901559E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>0.426700550271565</v>
+      </c>
+      <c r="B88">
+        <v>4.8501692652509303E-2</v>
+      </c>
+      <c r="C88" s="5">
+        <v>0.56359607348809704</v>
+      </c>
+      <c r="D88" s="4">
+        <v>8.7626734248610703E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>0.32145832557302401</v>
+      </c>
+      <c r="B89">
+        <v>-4.9065919825311E-2</v>
+      </c>
+      <c r="C89" s="5">
+        <v>0.54287679616769402</v>
+      </c>
+      <c r="D89" s="4">
+        <v>-4.2382986283414102E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>0.36725213974703502</v>
+      </c>
+      <c r="B90">
+        <v>5.5411365821441801E-2</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0.44355011936713201</v>
+      </c>
+      <c r="D90" s="4">
+        <v>9.7055821140570306E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>0.214829891832057</v>
+      </c>
+      <c r="B91">
+        <v>6.4877611185017003E-2</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0.52444267272922795</v>
+      </c>
+      <c r="D91" s="6">
+        <v>0.12356499547022801</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>0.58169295649827502</v>
+      </c>
+      <c r="B92" s="2">
+        <v>0.136776779215773</v>
+      </c>
+      <c r="C92" s="5">
+        <v>1.3503826757847699</v>
+      </c>
+      <c r="D92" s="4">
+        <v>-0.111382648945121</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>0.81953983163651301</v>
+      </c>
+      <c r="B93">
+        <v>9.6248530792213197E-2</v>
+      </c>
+      <c r="C93" s="5">
+        <v>0.77640018539284195</v>
+      </c>
+      <c r="D93" s="6">
+        <v>0.12378670901094201</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>0.53043392800088496</v>
+      </c>
+      <c r="B94" s="2">
+        <v>1.8030593251305502E-2</v>
+      </c>
+      <c r="C94" s="5">
+        <v>0.70599426763784001</v>
+      </c>
+      <c r="D94" s="4">
+        <v>-4.0425661891099604E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>0.101752763399727</v>
+      </c>
+      <c r="B95" s="2">
+        <v>1.0114107463523399E-2</v>
+      </c>
+      <c r="C95" s="5">
+        <v>0.34777067777122</v>
+      </c>
+      <c r="D95" s="4">
+        <v>-3.8294594165612497E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>0.29759891163461299</v>
+      </c>
+      <c r="B96">
+        <v>2.15346897273439E-2</v>
+      </c>
+      <c r="C96" s="5">
+        <v>0.36003061601502401</v>
+      </c>
+      <c r="D96" s="4">
+        <v>3.2330256574929897E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>0.59379039238843201</v>
+      </c>
+      <c r="B97">
+        <v>6.8632746045060894E-2</v>
+      </c>
+      <c r="C97" s="5">
+        <v>0.90738654363118498</v>
+      </c>
+      <c r="D97" s="4">
+        <v>-2.99523177484513E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>0.19517173432969201</v>
+      </c>
+      <c r="B98">
+        <v>-1.07540846266662E-2</v>
+      </c>
+      <c r="C98" s="5">
+        <v>0.54157733797246899</v>
+      </c>
+      <c r="D98" s="6">
+        <v>1.33961301910032E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>0.294740324138479</v>
+      </c>
+      <c r="B99">
+        <v>4.02242312843646E-2</v>
+      </c>
+      <c r="C99" s="5">
+        <v>0.84833617879402001</v>
+      </c>
+      <c r="D99" s="6">
+        <v>0.105973747447243</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>0.21697918617360501</v>
+      </c>
+      <c r="B100" s="2">
+        <v>1.5131667649345501E-2</v>
+      </c>
+      <c r="C100" s="5">
+        <v>1.2315102796950499</v>
+      </c>
+      <c r="D100" s="4">
+        <v>2.2119748045636E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>0.39675788297376302</v>
+      </c>
+      <c r="B101">
+        <v>8.1945382570874897E-3</v>
+      </c>
+      <c r="C101" s="5">
+        <v>1.35743302631009</v>
+      </c>
+      <c r="D101" s="4">
+        <v>4.6830354540975403E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>0.28272235758507802</v>
+      </c>
+      <c r="B102">
+        <v>5.19329228246918E-2</v>
+      </c>
+      <c r="C102" s="5">
+        <v>0.62840111585278202</v>
+      </c>
+      <c r="D102" s="4">
+        <v>-8.8350400477990906E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>0.17653550981482999</v>
+      </c>
+      <c r="B103">
+        <v>4.1170269306558697E-2</v>
+      </c>
+      <c r="C103" s="5">
+        <v>0.69121065361350797</v>
+      </c>
+      <c r="D103" s="6">
+        <v>0.13523040710707801</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
+        <v>0.15999512064736099</v>
+      </c>
+      <c r="B104">
+        <v>-5.1106502665788298E-2</v>
+      </c>
+      <c r="C104" s="5">
+        <v>1.0825207222573701</v>
+      </c>
+      <c r="D104" s="4">
+        <v>-3.1315177302968303E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
+        <v>0.37712102256082802</v>
+      </c>
+      <c r="B105">
+        <v>4.1422714343459302E-2</v>
+      </c>
+      <c r="C105" s="5">
+        <v>0.370033179403015</v>
+      </c>
+      <c r="D105" s="4">
+        <v>-7.4314125011362295E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
+        <v>0.24993382397587899</v>
+      </c>
+      <c r="B106">
+        <v>3.0139700024107999E-2</v>
+      </c>
+      <c r="C106" s="5">
+        <v>-2.4553000000000001E-3</v>
+      </c>
+      <c r="D106" s="6">
+        <v>3.6780686806557002E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
+        <v>0.51900705654855805</v>
+      </c>
+      <c r="B107">
+        <v>8.6417614066849294E-2</v>
+      </c>
+      <c r="C107" s="5">
+        <v>0.15647311598245001</v>
+      </c>
+      <c r="D107" s="4">
+        <v>-1.5382496705559001E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
+        <v>0.30281959048772</v>
+      </c>
+      <c r="B108">
+        <v>-6.3786430198621499E-2</v>
+      </c>
+      <c r="C108" s="5">
+        <v>2.5858603673218E-2</v>
+      </c>
+      <c r="D108" s="4">
+        <v>-5.0962939029222003E-4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
+        <v>0.23293026064773301</v>
+      </c>
+      <c r="B109">
+        <v>-5.1414455146004998E-2</v>
+      </c>
+      <c r="C109" s="5">
+        <v>6.7398420000000001E-2</v>
+      </c>
+      <c r="D109" s="4">
+        <v>-8.5835999137573293E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
+        <v>0.29788455680176801</v>
+      </c>
+      <c r="B110" s="2">
+        <v>4.0697180845120202E-2</v>
+      </c>
+      <c r="C110" s="5">
+        <v>0.222159203452828</v>
+      </c>
+      <c r="D110" s="6">
+        <v>2.1263941504311198E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
+        <v>0.51789406780934899</v>
+      </c>
+      <c r="B111" s="2">
+        <v>5.42020419619475E-2</v>
+      </c>
+      <c r="C111" s="5">
+        <v>-2.8403299999999999E-2</v>
+      </c>
+      <c r="D111" s="4">
+        <v>-2.2331272587212701E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="2">
+        <v>0.68911392327477605</v>
+      </c>
+      <c r="B112">
+        <v>9.6509768628655498E-2</v>
+      </c>
+      <c r="C112" s="5">
+        <v>0.39723648932891797</v>
+      </c>
+      <c r="D112" s="4">
+        <v>4.2618224353279201E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="2">
+        <v>1.06777283534142</v>
+      </c>
+      <c r="B113">
+        <v>8.8703612937082996E-2</v>
+      </c>
+      <c r="C113" s="5">
+        <v>0.223022777425219</v>
+      </c>
+      <c r="D113" s="4">
+        <v>3.3393393280553997E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="2">
+        <v>0.121081587090583</v>
+      </c>
+      <c r="B114">
+        <v>-1.31229819235241E-2</v>
+      </c>
+      <c r="C114" s="5">
+        <v>3.3464179273612102E-2</v>
+      </c>
+      <c r="D114" s="4">
+        <v>-2.8612223700448299E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="2">
+        <v>0.35608196533884401</v>
+      </c>
+      <c r="B115">
+        <v>6.0122437880954296E-3</v>
+      </c>
+      <c r="C115" s="5">
+        <v>0.16420463821617401</v>
+      </c>
+      <c r="D115" s="6">
+        <v>1.37125589104944E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>0.54652787113469603</v>
+      </c>
+      <c r="B116">
+        <v>5.4974645091198801E-2</v>
+      </c>
+      <c r="C116" s="5">
+        <v>7.2986400000000007E-2</v>
+      </c>
+      <c r="D116" s="4">
+        <v>7.7569418892944999E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="2">
+        <v>0.75165753120498502</v>
+      </c>
+      <c r="B117">
+        <v>8.0931761701332997E-2</v>
+      </c>
+      <c r="C117" s="5">
+        <v>0.34514256672942101</v>
+      </c>
+      <c r="D117" s="4">
+        <v>-3.1379556428244399E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="2">
+        <v>0.32175711238452898</v>
+      </c>
+      <c r="B118" s="2">
+        <v>1.7804892522071999E-2</v>
+      </c>
+      <c r="C118" s="5">
+        <v>0.12910178606102199</v>
+      </c>
+      <c r="D118" s="4">
+        <v>-6.5550031393785395E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="2">
+        <v>0.64639665828546899</v>
+      </c>
+      <c r="B119">
+        <v>-5.5959315799126802E-2</v>
+      </c>
+      <c r="C119" s="5">
+        <v>-7.7074799999999999E-2</v>
+      </c>
+      <c r="D119" s="4">
+        <v>3.8997742276738002E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="2">
+        <v>0.55305346691199098</v>
+      </c>
+      <c r="B120">
+        <v>1.75204829092316E-2</v>
+      </c>
+      <c r="C120" s="5">
+        <v>0.218051804725303</v>
+      </c>
+      <c r="D120" s="6">
+        <v>2.3872233345015498E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="2">
+        <v>0.37913743498394897</v>
+      </c>
+      <c r="B121">
+        <v>3.1423459162828703E-2</v>
+      </c>
+      <c r="C121" s="5">
+        <v>0.111647709008003</v>
+      </c>
+      <c r="D121" s="4">
+        <v>-7.9661333053973396E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="2">
+        <v>0.76518373156385799</v>
+      </c>
+      <c r="B122">
+        <v>6.10039609259607E-2</v>
+      </c>
+      <c r="C122" s="5">
+        <v>-1.1784E-3</v>
+      </c>
+      <c r="D122" s="4">
+        <v>4.12838662399712E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="2">
+        <v>0.84696186701200304</v>
+      </c>
+      <c r="B123">
+        <v>-8.2149363296492896E-3</v>
+      </c>
+      <c r="C123" s="5">
+        <v>-6.4853599999999997E-2</v>
+      </c>
+      <c r="D123" s="4">
+        <v>-2.0702742996860798E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="2">
+        <v>0.66847813709889203</v>
+      </c>
+      <c r="B124" s="2">
+        <v>1.7649758497807502E-2</v>
+      </c>
+      <c r="C124" s="5">
+        <v>7.9944630000000003E-2</v>
+      </c>
+      <c r="D124" s="4">
+        <v>-2.0349029485519199E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="2">
+        <v>0.88469066403298102</v>
+      </c>
+      <c r="B125" s="2">
+        <v>0.101563667594068</v>
+      </c>
+      <c r="C125" s="5">
+        <v>2.7532439999999998E-2</v>
+      </c>
+      <c r="D125" s="4">
+        <v>-1.7558140161724502E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="2">
+        <v>0.65304007596381997</v>
+      </c>
+      <c r="B126">
+        <v>-6.8924967577523394E-2</v>
+      </c>
+      <c r="C126" s="5">
+        <v>0.11687245647047</v>
+      </c>
+      <c r="D126" s="4">
+        <v>-7.1046974194856E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="2">
+        <v>0.59729638609343505</v>
+      </c>
+      <c r="B127" s="2">
+        <v>4.2216944500859097E-2</v>
+      </c>
+      <c r="C127" s="5">
+        <v>-1.23681E-2</v>
+      </c>
+      <c r="D127" s="4">
+        <v>-1.46720608229711E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="2">
+        <v>1.16609964376023</v>
+      </c>
+      <c r="B128">
+        <v>-6.3680241604003499E-2</v>
+      </c>
+      <c r="C128" s="5">
+        <v>0.29656205355343601</v>
+      </c>
+      <c r="D128" s="6">
+        <v>5.2594268960577603E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="2">
+        <v>0.84658197442323302</v>
+      </c>
+      <c r="B129" s="2">
+        <v>0.113199232341071</v>
+      </c>
+      <c r="C129" s="5">
+        <v>0.52232089999999998</v>
+      </c>
+      <c r="D129" s="4">
+        <v>-9.9714217007800202E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="2">
+        <v>0.477708372696942</v>
+      </c>
+      <c r="B130">
+        <v>-3.5814570802799497E-2</v>
+      </c>
+      <c r="C130" s="5">
+        <v>-5.1698800000000003E-2</v>
+      </c>
+      <c r="D130" s="4">
+        <v>5.1657939783545902E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="2">
+        <v>0.71913494099860498</v>
+      </c>
+      <c r="B131">
+        <v>-6.7692941059807499E-2</v>
+      </c>
+      <c r="C131" s="5">
+        <v>0.39870168697628899</v>
+      </c>
+      <c r="D131" s="6">
+        <v>3.3094842619376799E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="2">
+        <v>1.1225043539838999</v>
+      </c>
+      <c r="B132">
+        <v>6.7055634258789895E-2</v>
+      </c>
+      <c r="C132" s="5">
+        <v>0.10071303543575499</v>
+      </c>
+      <c r="D132" s="4">
+        <v>9.792618596460819E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="2">
+        <v>0.45044172437388402</v>
+      </c>
+      <c r="B133">
+        <v>8.2184122460141298E-2</v>
+      </c>
+      <c r="C133" s="5">
+        <v>0.18345527036652801</v>
+      </c>
+      <c r="D133" s="6">
+        <v>1.89844096228368E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="2">
+        <v>0.69152944094540802</v>
+      </c>
+      <c r="B134">
+        <v>-2.93766618680113E-2</v>
+      </c>
+      <c r="C134" s="5">
+        <v>0.60571109944333101</v>
+      </c>
+      <c r="D134" s="4">
+        <v>-3.9551842380566998E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="2">
+        <v>0.56765844828976497</v>
+      </c>
+      <c r="B135">
+        <v>4.0645867912722899E-2</v>
+      </c>
+      <c r="C135" s="5">
+        <v>0.366924010030106</v>
+      </c>
+      <c r="D135" s="4">
+        <v>9.7838690316339294E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="2">
+        <v>0.32471018233107501</v>
+      </c>
+      <c r="B136">
+        <v>-1.04333315671171E-2</v>
+      </c>
+      <c r="C136" s="5">
+        <v>0.378731845705642</v>
+      </c>
+      <c r="D136" s="4">
+        <v>3.1710418891159602E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="2">
+        <v>1.1820257366251099</v>
+      </c>
+      <c r="B137">
+        <v>-4.5866173326452798E-2</v>
+      </c>
+      <c r="C137" s="5">
+        <v>0.66634230808412998</v>
+      </c>
+      <c r="D137" s="4">
+        <v>-5.3693114090150797E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="2">
+        <v>0.72135823272896504</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.118441256255589</v>
+      </c>
+      <c r="C138" s="5">
+        <v>0.371556377162856</v>
+      </c>
+      <c r="D138" s="4">
+        <v>3.9754367851454503E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="2">
+        <v>0.77125049291565995</v>
+      </c>
+      <c r="B139">
+        <v>-2.1424054185797299E-2</v>
+      </c>
+      <c r="C139" s="5">
+        <v>1.1319730073699501</v>
+      </c>
+      <c r="D139" s="4">
+        <v>6.18002830740483E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="2">
+        <v>0.68038252949459899</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.148666020706649</v>
+      </c>
+      <c r="C140" s="5">
+        <v>0.49208111086506101</v>
+      </c>
+      <c r="D140" s="4">
+        <v>2.46756619561087E-3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="2">
+        <v>0.84315378095067794</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.11341258944531001</v>
+      </c>
+      <c r="C141" s="5">
+        <v>0.60481974371551495</v>
+      </c>
+      <c r="D141" s="4">
+        <v>-2.6687137514084601E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="2">
+        <v>0.70892299452775298</v>
+      </c>
+      <c r="B142">
+        <v>8.9700143499440096E-2</v>
+      </c>
+      <c r="C142" s="5">
+        <v>0.56377186000000001</v>
+      </c>
+      <c r="D142" s="6">
+        <v>1.23970200979203E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="2">
+        <v>0.1100298148075</v>
+      </c>
+      <c r="B143">
+        <v>3.3531305601066899E-3</v>
+      </c>
+      <c r="C143" s="5">
+        <v>0.36409568868388498</v>
+      </c>
+      <c r="D143" s="6">
+        <v>1.3340104581288899E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="2">
+        <v>0.42348739961439802</v>
+      </c>
+      <c r="B144" s="2">
+        <v>6.1113893916638497E-2</v>
+      </c>
+      <c r="C144" s="5">
+        <v>0.33023733999999999</v>
+      </c>
+      <c r="D144" s="4">
+        <v>-2.8338871339965498E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="2">
+        <v>0.38520720556890797</v>
+      </c>
+      <c r="B145" s="2">
+        <v>4.5235865006437698E-2</v>
+      </c>
+      <c r="C145" s="5">
+        <v>0.47521095641538003</v>
+      </c>
+      <c r="D145" s="4">
+        <v>-9.1647817803240494E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="2">
+        <v>0.69538019599605305</v>
+      </c>
+      <c r="B146">
+        <v>3.6501465895955199E-3</v>
+      </c>
+      <c r="C146" s="5">
+        <v>0.55231078883002305</v>
+      </c>
+      <c r="D146" s="4">
+        <v>-8.2534902871026702E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="2">
+        <v>0.46283307391113099</v>
+      </c>
+      <c r="B147">
+        <v>-5.22442299671982E-2</v>
+      </c>
+      <c r="C147" s="5">
+        <v>0.90552039853278599</v>
+      </c>
+      <c r="D147" s="4">
+        <v>6.1605144261997799E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>8.1463266946373902E-2</v>
+      </c>
+      <c r="B148">
+        <v>1.4098410228585399E-3</v>
+      </c>
+      <c r="C148" s="5">
+        <v>0.26169175364587</v>
+      </c>
+      <c r="D148" s="6">
+        <v>2.5688227226967002E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>0.85091225306694396</v>
+      </c>
+      <c r="B149" s="2">
+        <v>4.5834072888394597E-2</v>
+      </c>
+      <c r="C149" s="5">
+        <v>0.52478957882244504</v>
+      </c>
+      <c r="D149" s="4">
+        <v>-5.3028976524293597E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>9.7225465571623093E-2</v>
+      </c>
+      <c r="B150">
+        <v>7.0932944992775498E-2</v>
+      </c>
+      <c r="C150" s="5">
+        <v>0.68145035354972205</v>
+      </c>
+      <c r="D150" s="4">
+        <v>-8.1010630686376203E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="2">
+        <v>0.28533089241764498</v>
+      </c>
+      <c r="B151">
+        <v>-2.92981151470646E-2</v>
+      </c>
+      <c r="C151" s="5">
+        <v>1.1290537628233499</v>
+      </c>
+      <c r="D151" s="6">
+        <v>2.1437989011811799E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="2">
+        <v>0.13405370343414699</v>
+      </c>
+      <c r="B152">
+        <v>-3.7237196637382002E-2</v>
+      </c>
+      <c r="C152" s="5">
+        <v>0.44459504</v>
+      </c>
+      <c r="D152" s="4">
+        <v>-6.0331761517187998E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="2">
+        <v>0.342966573540468</v>
+      </c>
+      <c r="B153">
+        <v>4.5273325518311501E-2</v>
+      </c>
+      <c r="C153" s="5">
+        <v>1.0805808310654501</v>
+      </c>
+      <c r="D153" s="4">
+        <v>-9.0002780504131893E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="2">
+        <v>0.69309057719372702</v>
+      </c>
+      <c r="B154">
+        <v>-1.49274685662509E-2</v>
+      </c>
+      <c r="C154" s="5">
+        <v>0.54354326629579797</v>
+      </c>
+      <c r="D154" s="4">
+        <v>-2.6342958566701501E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="2">
+        <v>0.26456327868187601</v>
+      </c>
+      <c r="B155">
+        <v>-3.2151823211700598E-2</v>
+      </c>
+      <c r="C155" s="5">
+        <v>0.817340300137961</v>
+      </c>
+      <c r="D155" s="4">
+        <v>-4.6693646041020803E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="2">
+        <v>0.644345637124906</v>
+      </c>
+      <c r="B156">
+        <v>3.07815543377635E-2</v>
+      </c>
+      <c r="C156" s="5">
+        <v>0.30596509540178102</v>
+      </c>
+      <c r="D156" s="4">
+        <v>-1.34926174518479E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="2">
+        <v>0.36577151894584298</v>
+      </c>
+      <c r="B157">
+        <v>9.5009569647007495E-3</v>
+      </c>
+      <c r="C157" s="5">
+        <v>0.98271612156189503</v>
+      </c>
+      <c r="D157" s="4">
+        <v>-2.3601320530538799E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="2">
+        <v>0.31154979210823203</v>
+      </c>
+      <c r="B158">
+        <v>-3.8577747792370498E-2</v>
+      </c>
+      <c r="C158" s="5">
+        <v>0.600927241246347</v>
+      </c>
+      <c r="D158" s="4">
+        <v>-5.6158249594179801E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" s="2">
+        <v>0.95175163178266498</v>
+      </c>
+      <c r="B159">
+        <v>9.7815177593529104E-2</v>
+      </c>
+      <c r="C159" s="5">
+        <v>0.43168638138443</v>
+      </c>
+      <c r="D159" s="4">
+        <v>-5.1543130457868201E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>-4.3032614002854498E-2</v>
+      </c>
+      <c r="B160" s="2">
+        <v>0.139477132348578</v>
+      </c>
+      <c r="C160" s="5">
+        <v>0.34820957261653601</v>
+      </c>
+      <c r="D160" s="4">
+        <v>-1.44555902109603E-2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" s="2">
+        <v>2.5124148238160199E-2</v>
+      </c>
+      <c r="B161">
+        <v>-1.4627170589830801E-2</v>
+      </c>
+      <c r="C161" s="5">
+        <v>0.26809940305338298</v>
+      </c>
+      <c r="D161" s="4">
+        <v>8.5943854619173303E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="2">
+        <v>0.40884774642684302</v>
+      </c>
+      <c r="B162">
+        <v>9.10775935139648E-2</v>
+      </c>
+      <c r="C162" s="5">
+        <v>0.77965869121077802</v>
+      </c>
+      <c r="D162" s="4">
+        <v>-7.5658799735376994E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="2">
+        <v>0.31576973455563101</v>
+      </c>
+      <c r="B163">
+        <v>-1.54538468267564E-2</v>
+      </c>
+      <c r="C163" s="5">
+        <v>0.45448183769386402</v>
+      </c>
+      <c r="D163" s="4">
+        <v>5.0231490262475703E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="2">
+        <v>0.32837748546277401</v>
+      </c>
+      <c r="B164">
+        <v>1.9918621500397499E-2</v>
+      </c>
+      <c r="C164" s="5">
+        <v>1.01717112760383</v>
+      </c>
+      <c r="D164" s="4">
+        <v>-8.1493873022433994E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>6.9272989648604996E-2</v>
+      </c>
+      <c r="B165" s="2">
+        <v>2.4510600953236102E-2</v>
+      </c>
+      <c r="C165" s="5">
+        <v>0.37621621489257301</v>
+      </c>
+      <c r="D165" s="4">
+        <v>-9.8124565661966996E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="2">
+        <v>0.351858583948017</v>
+      </c>
+      <c r="B166" s="2">
+        <v>1.5179261482751999E-2</v>
+      </c>
+      <c r="C166" s="5">
+        <v>0.282178304019992</v>
+      </c>
+      <c r="D166" s="4">
+        <v>-2.82625291184504E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>0.904789615731588</v>
+      </c>
+      <c r="B167" s="2">
+        <v>0.10963082111735201</v>
+      </c>
+      <c r="C167" s="5">
+        <v>0.73015254309115496</v>
+      </c>
+      <c r="D167" s="4">
+        <v>-3.4740589669661898E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="2">
+        <v>0.73688230910758001</v>
+      </c>
+      <c r="B168">
+        <v>4.3376604955988697E-2</v>
+      </c>
+      <c r="C168" s="5">
+        <v>0.77473854217584104</v>
+      </c>
+      <c r="D168" s="6">
+        <v>4.1562927801749701E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="2">
+        <v>0.49210873248158099</v>
+      </c>
+      <c r="B169" s="2">
+        <v>5.3992216131109202E-2</v>
+      </c>
+      <c r="C169" s="5">
+        <v>0.61004784000000001</v>
+      </c>
+      <c r="D169" s="4">
+        <v>-0.11001235914002901</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="2">
+        <v>0.38432408302030402</v>
+      </c>
+      <c r="B170">
+        <v>-8.4451361953392604E-2</v>
+      </c>
+      <c r="C170" s="5">
+        <v>1.0825594161726</v>
+      </c>
+      <c r="D170" s="4">
+        <v>-4.8598362744142302E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="2">
+        <v>0.312441738648013</v>
+      </c>
+      <c r="B171">
+        <v>-8.3099670865231498E-2</v>
+      </c>
+      <c r="C171" s="5">
+        <v>0.13256572233625599</v>
+      </c>
+      <c r="D171" s="4">
+        <v>-8.7061733096312793E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="2">
+        <v>1.51048660754056E-2</v>
+      </c>
+      <c r="B172">
+        <v>7.7848549280531407E-2</v>
+      </c>
+      <c r="C172" s="5">
+        <v>0.69075978000000005</v>
+      </c>
+      <c r="D172" s="4">
+        <v>5.7117881864525301E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="2">
+        <v>0.176633995907757</v>
+      </c>
+      <c r="B173">
+        <v>9.5829274931043401E-2</v>
+      </c>
+      <c r="C173" s="5">
+        <v>1.0422400141794399</v>
+      </c>
+      <c r="D173" s="4">
+        <v>-3.73943600753813E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="2">
+        <v>0.17084485719812301</v>
+      </c>
+      <c r="B174">
+        <v>9.8688476873195097E-2</v>
+      </c>
+      <c r="C174" s="5">
+        <v>0.70513880236388804</v>
+      </c>
+      <c r="D174" s="4">
+        <v>-4.5492761456006198E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="2">
+        <v>0.28301774446390698</v>
+      </c>
+      <c r="B175">
+        <v>4.6880573105819202E-2</v>
+      </c>
+      <c r="C175" s="5">
+        <v>0.42900702341222402</v>
+      </c>
+      <c r="D175" s="4">
+        <v>3.7244396249698601E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="2">
+        <v>0.205852301466561</v>
+      </c>
+      <c r="B176">
+        <v>-2.3336645051841E-2</v>
+      </c>
+      <c r="C176" s="5">
+        <v>0.81772518340491995</v>
+      </c>
+      <c r="D176" s="4">
+        <v>-0.120126244499794</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="2">
+        <v>0.49680633769585197</v>
+      </c>
+      <c r="B177">
+        <v>8.9648275114881798E-2</v>
+      </c>
+      <c r="C177" s="5">
+        <v>-8.1378099999999995E-2</v>
+      </c>
+      <c r="D177" s="4">
+        <v>-6.3466289276154594E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="2">
+        <v>0.31992807436147602</v>
+      </c>
+      <c r="B178" s="2">
+        <v>5.6688491782567997E-2</v>
+      </c>
+      <c r="C178" s="5">
+        <v>0.63403193781973599</v>
+      </c>
+      <c r="D178" s="4">
+        <v>3.01300473481971E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="2">
+        <v>0.58971616020569495</v>
+      </c>
+      <c r="B179" s="2">
+        <v>0.118791463215808</v>
+      </c>
+      <c r="C179" s="5">
+        <v>0.93957945379485097</v>
+      </c>
+      <c r="D179" s="4">
+        <v>-6.8507303022660102E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>-7.6590701353427297E-3</v>
+      </c>
+      <c r="B180" s="2">
+        <v>3.0965506200065201E-2</v>
+      </c>
+      <c r="C180" s="5">
+        <v>0.67220500180336995</v>
+      </c>
+      <c r="D180" s="4">
+        <v>-8.9898639107014205E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="2">
+        <v>0.47539499233713001</v>
+      </c>
+      <c r="B181">
+        <v>5.8521138378839502E-2</v>
+      </c>
+      <c r="C181" s="5">
+        <v>0.66037134426508204</v>
+      </c>
+      <c r="D181" s="4">
+        <v>-6.1458651983012001E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="2">
+        <v>0.28143772983250698</v>
+      </c>
+      <c r="B182" s="2">
+        <v>0.13016024686289601</v>
+      </c>
+      <c r="C182" s="5">
+        <v>0.92914342801683303</v>
+      </c>
+      <c r="D182" s="4">
+        <v>-4.5442196531665898E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" s="2">
+        <v>0.16969639621511901</v>
+      </c>
+      <c r="B183" s="2">
+        <v>4.85485477059747E-2</v>
+      </c>
+      <c r="C183" s="5">
+        <v>0.52149843362904602</v>
+      </c>
+      <c r="D183" s="4">
+        <v>-4.6487264645722101E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" s="2">
+        <v>0.392084310510871</v>
+      </c>
+      <c r="B184" s="2">
+        <v>2.10973227032808E-2</v>
+      </c>
+      <c r="C184" s="5">
+        <v>1.00922161429795</v>
+      </c>
+      <c r="D184" s="4">
+        <v>-5.73498815327457E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" s="2">
+        <v>0.49747116852312601</v>
+      </c>
+      <c r="B185" s="2">
+        <v>4.2673302928456697E-2</v>
+      </c>
+      <c r="C185" s="5">
+        <v>0.61632776888846397</v>
+      </c>
+      <c r="D185" s="4">
+        <v>-4.3666590170988499E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>1.7272784627376199E-2</v>
+      </c>
+      <c r="B186">
+        <v>3.85923647932266E-2</v>
+      </c>
+      <c r="C186" s="5">
+        <v>0.55371459000000001</v>
+      </c>
+      <c r="D186" s="4">
+        <v>-6.0611166514024E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>0.13872675069667301</v>
+      </c>
+      <c r="B187" s="2">
+        <v>2.9765758709083399E-2</v>
+      </c>
+      <c r="C187" s="5">
+        <v>0.33858977865850898</v>
+      </c>
+      <c r="D187" s="4">
+        <v>1.3143750224453901E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" s="2">
+        <v>0.37301813885906399</v>
+      </c>
+      <c r="B188" s="2">
+        <v>0.101886410221233</v>
+      </c>
+      <c r="C188" s="5">
+        <v>0.55035065000000005</v>
+      </c>
+      <c r="D188" s="4">
+        <v>6.1057219232104797E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" s="2">
+        <v>0.25863494020019701</v>
+      </c>
+      <c r="B189">
+        <v>5.79307116400078E-2</v>
+      </c>
+      <c r="C189" s="5">
+        <v>0.319216572510512</v>
+      </c>
+      <c r="D189" s="4">
+        <v>-4.35985564388107E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" s="2">
+        <v>0.63424728891957005</v>
+      </c>
+      <c r="B190" s="2">
+        <v>3.2116827970554498E-2</v>
+      </c>
+      <c r="C190" s="5">
+        <v>0.79413565985947199</v>
+      </c>
+      <c r="D190" s="4">
+        <v>7.6276703337502597E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" s="2">
+        <v>1.0066848404604301</v>
+      </c>
+      <c r="B191">
+        <v>-4.7768514519680602E-2</v>
+      </c>
+      <c r="C191" s="5">
+        <v>0.98425942744410799</v>
+      </c>
+      <c r="D191" s="4">
+        <v>-8.0135721179502004E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" s="2">
+        <v>0.41859170621520903</v>
+      </c>
+      <c r="B192">
+        <v>3.1037349599234602E-2</v>
+      </c>
+      <c r="C192" s="5">
+        <v>0.59162525453806403</v>
+      </c>
+      <c r="D192" s="4">
+        <v>-2.00860885299541E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" s="2">
+        <v>0.67539624145994404</v>
+      </c>
+      <c r="B193">
+        <v>8.7661504452243702E-2</v>
+      </c>
+      <c r="C193" s="5">
+        <v>0.54611841000000005</v>
+      </c>
+      <c r="D193" s="6">
+        <v>0.129036934885399</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" s="2">
+        <v>0.252213898947653</v>
+      </c>
+      <c r="B194">
+        <v>-2.6306642551384402E-2</v>
+      </c>
+      <c r="C194" s="5">
+        <v>0.89822974295676405</v>
+      </c>
+      <c r="D194" s="4">
+        <v>-3.5915819702727697E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" s="2">
+        <v>0.54126214237838999</v>
+      </c>
+      <c r="B195">
+        <v>7.0217076075168E-2</v>
+      </c>
+      <c r="C195" s="5">
+        <v>1.0472458107839799</v>
+      </c>
+      <c r="D195" s="4">
+        <v>-1.7043586098054599E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" s="2">
+        <v>0.84025978746924601</v>
+      </c>
+      <c r="B196">
+        <v>6.6808697433058506E-2</v>
+      </c>
+      <c r="C196" s="5">
+        <v>0.65476615009865202</v>
+      </c>
+      <c r="D196" s="4">
+        <v>-0.105780484370721</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="2">
+        <v>0.90252810138599304</v>
+      </c>
+      <c r="B197">
+        <v>-1.42723400499653E-3</v>
+      </c>
+      <c r="C197" s="5">
+        <v>0.51174808691005003</v>
+      </c>
+      <c r="D197" s="4">
+        <v>7.8035855145277104E-3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>0.786116757757927</v>
+      </c>
+      <c r="B198" s="2">
+        <v>0.13290040101270401</v>
+      </c>
+      <c r="C198" s="5">
+        <v>0.67402327392473005</v>
+      </c>
+      <c r="D198" s="4">
+        <v>3.3759462313164901E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="2">
+        <v>0.51359669100386496</v>
+      </c>
+      <c r="B199" s="2">
+        <v>1.6345154889504099E-2</v>
+      </c>
+      <c r="C199" s="5">
+        <v>0.28668894150820601</v>
+      </c>
+      <c r="D199" s="4">
+        <v>-4.4122516540613499E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="2">
+        <v>0.495769204316029</v>
+      </c>
+      <c r="B200">
+        <v>-8.6822706890438694E-3</v>
+      </c>
+      <c r="C200" s="5">
+        <v>0.88669177271537802</v>
+      </c>
+      <c r="D200" s="6">
+        <v>1.9323895753920999E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="2">
+        <v>0.90364153325593</v>
+      </c>
+      <c r="B201" s="2">
+        <v>0.13783986366256601</v>
+      </c>
+      <c r="C201" s="5">
+        <v>0.72017254609515402</v>
+      </c>
+      <c r="D201" s="4">
+        <v>5.9180487429427803E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="2">
+        <v>0.64514969933124799</v>
+      </c>
+      <c r="B202">
+        <v>-8.7601986957253394E-2</v>
+      </c>
+      <c r="C202" s="5">
+        <v>0.782344568816844</v>
+      </c>
+      <c r="D202" s="4">
+        <v>1.89414676079038E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" s="2">
+        <v>1.03037079951438</v>
+      </c>
+      <c r="B203">
+        <v>9.3715931265139593E-2</v>
+      </c>
+      <c r="C203" s="5">
+        <v>0.61947668949636103</v>
+      </c>
+      <c r="D203" s="6">
+        <v>3.6271890443629003E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" s="2">
+        <v>0.62571022746153704</v>
+      </c>
+      <c r="B204">
+        <v>5.47174626961607E-2</v>
+      </c>
+      <c r="C204" s="5">
+        <v>1.0689053978741001</v>
+      </c>
+      <c r="D204" s="6">
+        <v>0.111887566203693</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" s="2">
+        <v>0.112824817025742</v>
+      </c>
+      <c r="B205">
+        <v>-3.0501541079715401E-2</v>
+      </c>
+      <c r="C205" s="5">
+        <v>0.57390103176935103</v>
+      </c>
+      <c r="D205" s="6">
+        <v>5.1732785229205998E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>0.57424016740398698</v>
+      </c>
+      <c r="B206" s="2">
+        <v>1.20787825541727E-2</v>
+      </c>
+      <c r="C206" s="5">
+        <v>1.0861821951358299</v>
+      </c>
+      <c r="D206" s="4">
+        <v>6.3622370401533604E-3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>0.93419945427190498</v>
+      </c>
+      <c r="B207">
+        <v>7.7114371879965601E-2</v>
+      </c>
+      <c r="C207" s="5">
+        <v>0.78828560614173804</v>
+      </c>
+      <c r="D207" s="4">
+        <v>4.3303341562837697E-3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A208" s="2">
+        <v>1.03640704496807</v>
+      </c>
+      <c r="B208" s="2">
+        <v>0.15385597727922901</v>
+      </c>
+      <c r="C208" s="5">
+        <v>0.40845541607387997</v>
+      </c>
+      <c r="D208" s="4">
+        <v>3.2235999162544E-2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A209" s="2">
+        <v>0.72568902406189895</v>
+      </c>
+      <c r="B209" s="2">
+        <v>0.14220372824806199</v>
+      </c>
+      <c r="C209" s="5">
+        <v>1.0409900705567301</v>
+      </c>
+      <c r="D209" s="6">
+        <v>2.2704079296219801E-2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>0.46262714794924198</v>
+      </c>
+      <c r="B210">
+        <v>5.6832925564515198E-2</v>
+      </c>
+      <c r="C210" s="5">
+        <v>0.44378918000000001</v>
+      </c>
+      <c r="D210" s="4">
+        <v>-3.7417321769462102E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A211" s="2">
+        <v>0.44294200634901898</v>
+      </c>
+      <c r="B211">
+        <v>3.5133531238621999E-3</v>
+      </c>
+      <c r="C211" s="5">
+        <v>0.53569895858785299</v>
+      </c>
+      <c r="D211" s="4">
+        <v>-1.1880501867495201E-2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A212" s="2">
+        <v>0.63057994170832099</v>
+      </c>
+      <c r="B212" s="2">
+        <v>0.14731454212758499</v>
+      </c>
+      <c r="C212" s="5">
+        <v>0.33942204494789202</v>
+      </c>
+      <c r="D212" s="4">
+        <v>8.5210845482762407E-2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A213" s="2">
+        <v>0.66462281171930304</v>
+      </c>
+      <c r="B213">
+        <v>6.5522570039378003E-2</v>
+      </c>
+      <c r="C213" s="5">
+        <v>0.93579131999999998</v>
+      </c>
+      <c r="D213" s="4">
+        <v>-2.1911176102477298E-2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A214" s="2">
+        <v>0.62566746411470198</v>
+      </c>
+      <c r="B214" s="2">
+        <v>0.12666758455025501</v>
+      </c>
+      <c r="C214" s="5">
+        <v>0.69532843</v>
+      </c>
+      <c r="D214" s="6">
+        <v>0.12803874378962599</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A215" s="2">
+        <v>0.64958318736191101</v>
+      </c>
+      <c r="B215">
+        <v>6.0393308298596201E-3</v>
+      </c>
+      <c r="C215" s="5">
+        <v>0.94394948485086205</v>
+      </c>
+      <c r="D215" s="4">
+        <v>-3.9432012522347397E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A216" s="2">
+        <v>0.54355771935979103</v>
+      </c>
+      <c r="B216" s="2">
+        <v>0.16975868933916199</v>
+      </c>
+      <c r="C216" s="5">
+        <v>0.80775384929058103</v>
+      </c>
+      <c r="D216" s="4">
+        <v>9.5033640752982401E-2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A217" s="2">
+        <v>0.861755955750101</v>
+      </c>
+      <c r="B217">
+        <v>4.5231252436848501E-2</v>
+      </c>
+      <c r="C217" s="5">
+        <v>1.07880994248912</v>
+      </c>
+      <c r="D217" s="4">
+        <v>6.2656555267709302E-2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A218" s="2">
+        <v>0.59170667401332799</v>
+      </c>
+      <c r="B218">
+        <v>5.6997538568919301E-2</v>
+      </c>
+      <c r="C218" s="5">
+        <v>0.37278810814672098</v>
+      </c>
+      <c r="D218" s="4">
+        <v>-4.7422934958371799E-2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A219" s="2">
+        <v>0.449553547725703</v>
+      </c>
+      <c r="B219">
+        <v>3.8356909784735799E-2</v>
+      </c>
+      <c r="C219" s="5">
+        <v>0.25133563902484302</v>
+      </c>
+      <c r="D219" s="4">
+        <v>-5.2868245617069702E-2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A220" s="2">
+        <v>0.44192911311324701</v>
+      </c>
+      <c r="B220" s="2">
+        <v>4.4307341704472897E-2</v>
+      </c>
+      <c r="C220" s="5">
+        <v>0.38452754687118901</v>
+      </c>
+      <c r="D220" s="4">
+        <v>2.2938678292202402E-2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A221" s="2">
+        <v>0.61090661058207396</v>
+      </c>
+      <c r="B221" s="2">
+        <v>5.8270665059201997E-2</v>
+      </c>
+      <c r="C221" s="5">
+        <v>1.12116465397882</v>
+      </c>
+      <c r="D221" s="4">
+        <v>4.9626359777094502E-2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222" s="2">
+        <v>0.66325438338726606</v>
+      </c>
+      <c r="B222">
+        <v>3.3511293559009801E-2</v>
+      </c>
+      <c r="C222" s="5">
+        <v>0.42753897920886402</v>
+      </c>
+      <c r="D222" s="4">
+        <v>-6.4399078473447197E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" s="2">
+        <v>0.50226932315443396</v>
+      </c>
+      <c r="B223">
+        <v>-3.8219031713805501E-2</v>
+      </c>
+      <c r="C223" s="5">
+        <v>0.86963357999472601</v>
+      </c>
+      <c r="D223" s="4">
+        <v>4.6212502828239001E-2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" s="2">
+        <v>0.78513095023325097</v>
+      </c>
+      <c r="B224">
+        <v>2.46690089616328E-2</v>
+      </c>
+      <c r="C224" s="5">
+        <v>0.70598043964011503</v>
+      </c>
+      <c r="D224" s="4">
+        <v>-0.102109032847959</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" s="2">
+        <v>0.48681748306475803</v>
+      </c>
+      <c r="B225">
+        <v>-6.3927500205994303E-2</v>
+      </c>
+      <c r="C225" s="5">
+        <v>0.15307432986511599</v>
+      </c>
+      <c r="D225" s="4">
+        <v>4.7179212178864102E-2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>0.36019089242101698</v>
+      </c>
+      <c r="B226">
+        <v>6.1925612003900697E-2</v>
+      </c>
+      <c r="C226" s="5">
+        <v>0.277576333176205</v>
+      </c>
+      <c r="D226" s="6">
+        <v>1.3071956259276299E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A227" s="2">
+        <v>0.88037362745157599</v>
+      </c>
+      <c r="B227">
+        <v>-2.8604766124708501E-2</v>
+      </c>
+      <c r="C227" s="5">
+        <v>0.44778278192002702</v>
+      </c>
+      <c r="D227" s="6">
+        <v>3.0300492403643901E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A228" s="2">
+        <v>0.54295861349114505</v>
+      </c>
+      <c r="B228" s="2">
+        <v>0.16833738174188201</v>
+      </c>
+      <c r="C228" s="5">
+        <v>0.72811894901715202</v>
+      </c>
+      <c r="D228" s="4">
+        <v>3.9098621799122497E-2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A229" s="2">
+        <v>0.87819998204378302</v>
+      </c>
+      <c r="B229" s="2">
+        <v>0.198620174384806</v>
+      </c>
+      <c r="C229" s="5">
+        <v>1.1842037736930699</v>
+      </c>
+      <c r="D229" s="4">
+        <v>-4.3942997752776996E-3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A230" s="2">
+        <v>0.55239721685936405</v>
+      </c>
+      <c r="B230">
+        <v>9.8152966516580301E-2</v>
+      </c>
+      <c r="C230" s="5">
+        <v>0.52759492182090595</v>
+      </c>
+      <c r="D230" s="4">
+        <v>-4.6163144436294204E-3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A231" s="2">
+        <v>0.79064062540371804</v>
+      </c>
+      <c r="B231" s="2">
+        <v>4.7164383145621797E-2</v>
+      </c>
+      <c r="C231" s="5">
+        <v>0.454557878215605</v>
+      </c>
+      <c r="D231" s="4">
+        <v>4.4493447058770903E-2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A232" s="2">
+        <v>0.44244987226013799</v>
+      </c>
+      <c r="B232">
+        <v>-1.32644675438226E-2</v>
+      </c>
+      <c r="C232" s="5">
+        <v>0.397506332311933</v>
+      </c>
+      <c r="D232" s="4">
+        <v>-4.7212698467910499E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A233" s="2">
+        <v>0.26182622476594403</v>
+      </c>
+      <c r="B233" s="2">
+        <v>0.120957325656926</v>
+      </c>
+      <c r="C233" s="5">
+        <v>0.53850093177053604</v>
+      </c>
+      <c r="D233" s="4">
+        <v>-1.2192848693224101E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A234" s="2">
+        <v>0.59250250536247995</v>
+      </c>
+      <c r="B234">
+        <v>-1.2681768236806701E-3</v>
+      </c>
+      <c r="C234" s="5">
+        <v>0.174328164223676</v>
+      </c>
+      <c r="D234" s="6">
+        <v>3.4943969756304802E-2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A235" s="2">
+        <v>0.34779886127862403</v>
+      </c>
+      <c r="B235" s="2">
+        <v>0.13630092561777701</v>
+      </c>
+      <c r="C235" s="5">
+        <v>0.31949524845843802</v>
+      </c>
+      <c r="D235" s="6">
+        <v>1.50006149600172E-2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A236" s="2">
+        <v>0.153991201020826</v>
+      </c>
+      <c r="B236">
+        <v>-2.41423280023472E-2</v>
+      </c>
+      <c r="C236" s="5">
+        <v>0.31674867373999899</v>
+      </c>
+      <c r="D236" s="4">
+        <v>-4.0261808878667198E-2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A237" s="2">
+        <v>0.51689713452979202</v>
+      </c>
+      <c r="B237">
+        <v>9.3543800591113502E-2</v>
+      </c>
+      <c r="C237" s="5">
+        <v>0.76706930236347004</v>
+      </c>
+      <c r="D237" s="4">
+        <v>-1.535308012024E-2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A238" s="2">
+        <v>0.44607994666578898</v>
+      </c>
+      <c r="B238" s="2">
+        <v>2.04959053721172E-2</v>
+      </c>
+      <c r="C238" s="5">
+        <v>0.74774238786191605</v>
+      </c>
+      <c r="D238" s="4">
+        <v>5.21065883974609E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A239" s="2">
+        <v>0.65174606029314697</v>
+      </c>
+      <c r="B239">
+        <v>-4.1143308075838499E-2</v>
+      </c>
+      <c r="C239" s="5">
+        <v>0.612010486153586</v>
+      </c>
+      <c r="D239" s="6">
+        <v>1.27458622068533E-2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A240" s="2">
+        <v>0.251771465418624</v>
+      </c>
+      <c r="B240" s="2">
+        <v>3.00875233250067E-2</v>
+      </c>
+      <c r="C240" s="5">
+        <v>0.51215845435233798</v>
+      </c>
+      <c r="D240" s="4">
+        <v>-9.6169306785842505E-3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A241" s="2">
+        <v>0.62469712342067196</v>
+      </c>
+      <c r="B241" s="2">
+        <v>0.120334913995015</v>
+      </c>
+      <c r="C241" s="5">
+        <v>0.55957529154775298</v>
+      </c>
+      <c r="D241" s="4">
+        <v>-2.5969788045974601E-3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242" s="2">
+        <v>0.33032842385038402</v>
+      </c>
+      <c r="B242">
+        <v>8.3970811558472205E-2</v>
+      </c>
+      <c r="C242" s="5">
+        <v>0.341681668328641</v>
+      </c>
+      <c r="D242" s="4">
+        <v>-1.8054696098252099E-2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243" s="2">
+        <v>0.32821739666102601</v>
+      </c>
+      <c r="B243">
+        <v>6.1596108099341497E-2</v>
+      </c>
+      <c r="C243" s="5">
+        <v>0.28400726382434999</v>
+      </c>
+      <c r="D243" s="6">
+        <v>1.5042593842064101E-2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244" s="2">
+        <v>0.23070371926681699</v>
+      </c>
+      <c r="B244" s="2">
+        <v>0.132967693367505</v>
+      </c>
+      <c r="C244" s="5">
+        <v>0.73673702386191098</v>
+      </c>
+      <c r="D244" s="4">
+        <v>-1.5635407760007498E-2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" s="2">
+        <v>0.64102402637733502</v>
+      </c>
+      <c r="B245" s="2">
+        <v>0.107198037860246</v>
+      </c>
+      <c r="C245" s="5">
+        <v>0.500941206022537</v>
+      </c>
+      <c r="D245" s="4">
+        <v>6.3612136955567503E-3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" s="2">
+        <v>0.304391903595917</v>
+      </c>
+      <c r="B246" s="2">
+        <v>0.10228470614674599</v>
+      </c>
+      <c r="C246" s="5">
+        <v>0.95783537336546598</v>
+      </c>
+      <c r="D246" s="4">
+        <v>-6.6269100246055507E-2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" s="2">
+        <v>0.46614646071121002</v>
+      </c>
+      <c r="B247" s="2">
+        <v>0.104467175990161</v>
+      </c>
+      <c r="C247" s="5">
+        <v>1.18445747148284</v>
+      </c>
+      <c r="D247" s="4">
+        <v>6.3670842329969196E-2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" s="2">
+        <v>0.66602972232647695</v>
+      </c>
+      <c r="B248">
+        <v>9.0430414013077207E-2</v>
+      </c>
+      <c r="C248" s="5">
+        <v>0.33762349000000003</v>
+      </c>
+      <c r="D248" s="4">
+        <v>-6.8627678942998094E-2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" s="2">
+        <v>1.1569373916077901</v>
+      </c>
+      <c r="B249">
+        <v>-1.6774297101571099E-2</v>
+      </c>
+      <c r="C249" s="5">
+        <v>0.28155246606894901</v>
+      </c>
+      <c r="D249" s="6">
+        <v>2.8677763756091101E-2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" s="2">
+        <v>0.44454051683162299</v>
+      </c>
+      <c r="B250" s="2">
+        <v>2.03565831739746E-2</v>
+      </c>
+      <c r="C250" s="5">
+        <v>0.57910241645741001</v>
+      </c>
+      <c r="D250" s="4">
+        <v>-1.2170013384734901E-2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A251" s="2">
+        <v>0.33399739855764699</v>
+      </c>
+      <c r="B251">
+        <v>-1.55487598605737E-2</v>
+      </c>
+      <c r="C251" s="5">
+        <v>0.63212816999999999</v>
+      </c>
+      <c r="D251" s="4">
+        <v>-8.3242477017654096E-3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>0.67413095662973799</v>
+      </c>
+      <c r="B252">
+        <v>7.7635897371370499E-2</v>
+      </c>
+      <c r="C252" s="5">
+        <v>0.58851829927075605</v>
+      </c>
+      <c r="D252" s="4">
+        <v>-1.09714811099943E-2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253" s="2">
+        <v>1.10936232296032</v>
+      </c>
+      <c r="B253">
+        <v>-4.9597334040822803E-2</v>
+      </c>
+      <c r="C253" s="5">
+        <v>0.58462514402090904</v>
+      </c>
+      <c r="D253" s="6">
+        <v>1.16682151243938E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A254" s="2">
+        <v>0.78602785139785603</v>
+      </c>
+      <c r="B254" s="2">
+        <v>0.14598616894650099</v>
+      </c>
+      <c r="C254" s="5">
+        <v>1.22538964870689</v>
+      </c>
+      <c r="D254" s="6">
+        <v>1.8120253782534599E-2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A255" s="2">
+        <v>0.57212312731760695</v>
+      </c>
+      <c r="B255">
+        <v>-4.6523732881396503E-2</v>
+      </c>
+      <c r="C255" s="5">
+        <v>5.8036110000000002E-2</v>
+      </c>
+      <c r="D255" s="4">
+        <v>-7.8114430308305503E-3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A256" s="2">
+        <v>0.35244994042057598</v>
+      </c>
+      <c r="B256">
+        <v>2.2188736048790899E-2</v>
+      </c>
+      <c r="C256" s="5">
+        <v>0.69547085692766697</v>
+      </c>
+      <c r="D256" s="4">
+        <v>1.42394073077159E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A257" s="2">
+        <v>0.28905258205314499</v>
+      </c>
+      <c r="B257">
+        <v>7.6532861998702701E-3</v>
+      </c>
+      <c r="C257" s="5">
+        <v>0.83195348000000002</v>
+      </c>
+      <c r="D257" s="4">
+        <v>5.5375646231431201E-2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A258" s="2">
+        <v>0.36976748614635702</v>
+      </c>
+      <c r="B258">
+        <v>7.0484648177783299E-2</v>
+      </c>
+      <c r="C258" s="5">
+        <v>1.0650581307640099</v>
+      </c>
+      <c r="D258" s="4">
+        <v>-1.51580870390543E-2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A259" s="2">
+        <v>0.47896260655184297</v>
+      </c>
+      <c r="B259">
+        <v>3.3503738798556199E-2</v>
+      </c>
+      <c r="C259" s="5">
+        <v>0.73585595000000004</v>
+      </c>
+      <c r="D259" s="4">
+        <v>-2.96013608787692E-2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A260" s="2">
+        <v>0.19029813383540201</v>
+      </c>
+      <c r="B260">
+        <v>-4.4074788190835198E-2</v>
+      </c>
+      <c r="C260" s="5">
+        <v>0.830216869427291</v>
+      </c>
+      <c r="D260" s="6">
+        <v>0.106428378442604</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A261" s="2">
+        <v>0.31755585901794198</v>
+      </c>
+      <c r="B261">
+        <v>7.2634938399130197E-2</v>
+      </c>
+      <c r="C261" s="5">
+        <v>0.74141621999999996</v>
+      </c>
+      <c r="D261" s="4">
+        <v>-0.100951061113442</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A262" s="2">
+        <v>1.06869313099092</v>
+      </c>
+      <c r="B262" s="2">
+        <v>3.8274977891040202E-2</v>
+      </c>
+      <c r="C262" s="5">
+        <v>0.81874788778692797</v>
+      </c>
+      <c r="D262" s="6">
+        <v>1.8655751950723099E-2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A263" s="2">
+        <v>0.50373273359894799</v>
+      </c>
+      <c r="B263">
+        <v>8.1104667905253197E-2</v>
+      </c>
+      <c r="C263" s="5">
+        <v>0.75957577994240799</v>
+      </c>
+      <c r="D263" s="4">
+        <v>8.1434850982779E-2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A264" s="2">
+        <v>1.0288180244871901</v>
+      </c>
+      <c r="B264" s="2">
+        <v>0.167952433892887</v>
+      </c>
+      <c r="C264" s="5">
+        <v>0.49073639239378403</v>
+      </c>
+      <c r="D264" s="4">
+        <v>-2.84738766014777E-2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A265" s="2">
+        <v>0.82453983050647495</v>
+      </c>
+      <c r="B265">
+        <v>4.6851036318382999E-2</v>
+      </c>
+      <c r="C265" s="5">
+        <v>0.75620771108266605</v>
+      </c>
+      <c r="D265" s="4">
+        <v>4.0994030147689098E-2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A266" s="2">
+        <v>0.43332529325396502</v>
+      </c>
+      <c r="B266" s="2">
+        <v>2.17590906431551E-2</v>
+      </c>
+      <c r="C266" s="5">
+        <v>1.1776833380153999</v>
+      </c>
+      <c r="D266" s="4">
+        <v>-2.2919099374030999E-2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A267" s="2">
+        <v>0.194340614140008</v>
+      </c>
+      <c r="B267" s="2">
+        <v>6.0391036060148999E-2</v>
+      </c>
+      <c r="C267" s="5">
+        <v>0.66457293236762804</v>
+      </c>
+      <c r="D267" s="4">
+        <v>-2.89291497449044E-2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A268" s="2">
+        <v>0.23653316425635099</v>
+      </c>
+      <c r="B268">
+        <v>3.48219658650136E-3</v>
+      </c>
+      <c r="C268" s="5">
+        <v>0.47342385681163801</v>
+      </c>
+      <c r="D268" s="4">
+        <v>2.5197164590451199E-2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A269" s="2">
+        <v>0.1698827915676</v>
+      </c>
+      <c r="B269">
+        <v>-1.8459561842650699E-2</v>
+      </c>
+      <c r="C269" s="5">
+        <v>1.0067484099999999</v>
+      </c>
+      <c r="D269" s="6">
+        <v>4.4919502470972997E-2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>5.80095980288192E-2</v>
+      </c>
+      <c r="B270">
+        <v>-6.13020914857983E-3</v>
+      </c>
+      <c r="C270" s="5">
+        <v>0.87154580000000004</v>
+      </c>
+      <c r="D270" s="4">
+        <v>8.5007635253790806E-2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A271" s="2">
+        <v>0.29039784230194299</v>
+      </c>
+      <c r="B271">
+        <v>4.7332483260466102E-2</v>
+      </c>
+      <c r="C271" s="5">
+        <v>0.55218963943676502</v>
+      </c>
+      <c r="D271" s="4">
+        <v>4.3717127707998101E-4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>4.99952670397966E-4</v>
+      </c>
+      <c r="B272" s="2">
+        <v>4.5926538596299499E-2</v>
+      </c>
+      <c r="C272" s="5">
+        <v>0.419627127189726</v>
+      </c>
+      <c r="D272" s="4">
+        <v>-1.3982836215179199E-2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>-1.3090691149583901E-2</v>
+      </c>
+      <c r="B273">
+        <v>7.9894896039576207E-3</v>
+      </c>
+      <c r="C273" s="5">
+        <v>0.911317031696392</v>
+      </c>
+      <c r="D273" s="4">
+        <v>-2.1145818685327E-2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A274" s="2">
+        <v>0.104267396394504</v>
+      </c>
+      <c r="B274">
+        <v>7.9080363514220903E-2</v>
+      </c>
+      <c r="C274" s="5">
+        <v>1.23273280570143</v>
+      </c>
+      <c r="D274" s="6">
+        <v>1.7532514745074501E-2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A275" s="2">
+        <v>0.23454329460090501</v>
+      </c>
+      <c r="B275" s="2">
+        <v>1.2959337885773E-2</v>
+      </c>
+      <c r="C275" s="5">
+        <v>0.20299639139685999</v>
+      </c>
+      <c r="D275" s="6">
+        <v>1.14269880331617E-2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A276" s="2">
+        <v>0.30240085220562901</v>
+      </c>
+      <c r="B276" s="2">
+        <v>1.4522722695608699E-2</v>
+      </c>
+      <c r="C276" s="5">
+        <v>0.80077298159911803</v>
+      </c>
+      <c r="D276" s="4">
+        <v>3.6255387380509603E-2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A277" s="2">
+        <v>0.68180544675884802</v>
+      </c>
+      <c r="B277">
+        <v>4.9155523971155697E-3</v>
+      </c>
+      <c r="C277" s="5">
+        <v>1.13843292195672</v>
+      </c>
+      <c r="D277" s="4">
+        <v>-1.9303302103750902E-2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A278" s="2">
+        <v>0.71452759770043806</v>
+      </c>
+      <c r="B278">
+        <v>-3.3525366763357899E-2</v>
+      </c>
+      <c r="C278" s="5">
+        <v>0.25940234399075601</v>
+      </c>
+      <c r="D278" s="4">
+        <v>-2.64484157867831E-2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A279" s="2">
+        <v>0.31995561839165698</v>
+      </c>
+      <c r="B279">
+        <v>6.9817745841607897E-3</v>
+      </c>
+      <c r="C279" s="5">
+        <v>0.530638027430967</v>
+      </c>
+      <c r="D279" s="6">
+        <v>1.0106562203619499E-2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A280" s="2">
+        <v>0.206389443782414</v>
+      </c>
+      <c r="B280">
+        <v>5.9094716199476698E-2</v>
+      </c>
+      <c r="C280" s="5">
+        <v>0.46977628301719299</v>
+      </c>
+      <c r="D280" s="4">
+        <v>-4.5541856225902497E-2</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>-1.8825924699837401E-2</v>
+      </c>
+      <c r="B281">
+        <v>6.17405802841553E-3</v>
+      </c>
+      <c r="C281" s="5">
+        <v>1.0606255366694699</v>
+      </c>
+      <c r="D281" s="4">
+        <v>2.77227989990016E-2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A282" s="2">
+        <v>0.200753684409956</v>
+      </c>
+      <c r="B282">
+        <v>4.3349133937336103E-2</v>
+      </c>
+      <c r="C282" s="5">
+        <v>0.18275343157032201</v>
+      </c>
+      <c r="D282" s="4">
+        <v>-3.7933747619533803E-2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A283" s="2">
+        <v>0.17014175502940901</v>
+      </c>
+      <c r="B283">
+        <v>6.6241389771006201E-2</v>
+      </c>
+      <c r="C283" s="5">
+        <v>1.1043695314877999</v>
+      </c>
+      <c r="D283" s="6">
+        <v>2.7488135097245799E-2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A284" s="2">
+        <v>0.23938301645725901</v>
+      </c>
+      <c r="B284">
+        <v>-3.9251395387092498E-2</v>
+      </c>
+      <c r="C284" s="5">
+        <v>0.40479312866959999</v>
+      </c>
+      <c r="D284" s="4">
+        <v>-2.4586609431688299E-2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A285" s="2">
+        <v>0.35240377045578702</v>
+      </c>
+      <c r="B285">
+        <v>6.1884123238726101E-3</v>
+      </c>
+      <c r="C285" s="5">
+        <v>0.186455019113067</v>
+      </c>
+      <c r="D285" s="4">
+        <v>-1.5151161218606501E-2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A286" s="2">
+        <v>0.37083421291130297</v>
+      </c>
+      <c r="B286">
+        <v>7.3250651917158795E-4</v>
+      </c>
+      <c r="C286" s="5">
+        <v>0.58809522442571804</v>
+      </c>
+      <c r="D286" s="6">
+        <v>0.114930692597218</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A287" s="2">
+        <v>0.64474383293901005</v>
+      </c>
+      <c r="B287">
+        <v>5.8438389776320203E-2</v>
+      </c>
+      <c r="C287" s="5">
+        <v>0.253709735685757</v>
+      </c>
+      <c r="D287" s="4">
+        <v>-4.3622916546811899E-2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A288" s="2">
+        <v>0.33541786459371298</v>
+      </c>
+      <c r="B288">
+        <v>-3.6430897811997702E-2</v>
+      </c>
+      <c r="C288" s="5">
+        <v>0.52096378897413098</v>
+      </c>
+      <c r="D288" s="4">
+        <v>-9.4930764935539702E-2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A289" s="2">
+        <v>0.23515170243587299</v>
+      </c>
+      <c r="B289" s="2">
+        <v>1.8226128267405099E-2</v>
+      </c>
+      <c r="C289" s="5">
+        <v>7.2575550000000003E-2</v>
+      </c>
+      <c r="D289" s="4">
+        <v>-6.5713745424723496E-2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A290" s="2">
+        <v>0.19684064597283499</v>
+      </c>
+      <c r="B290">
+        <v>-6.4784914685061798E-2</v>
+      </c>
+      <c r="C290" s="5">
+        <v>0.107226208462765</v>
+      </c>
+      <c r="D290" s="4">
+        <v>-9.0912175669245702E-3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A291" s="2">
+        <v>0.21237875990680199</v>
+      </c>
+      <c r="B291">
+        <v>-2.9281909640016899E-2</v>
+      </c>
+      <c r="C291" s="5">
+        <v>0.14564294042131701</v>
+      </c>
+      <c r="D291" s="4">
+        <v>2.68982896283367E-3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A292" s="2">
+        <v>0.461212050064503</v>
+      </c>
+      <c r="B292">
+        <v>5.6649653962406898E-2</v>
+      </c>
+      <c r="C292" s="5">
+        <v>0.46143037413516502</v>
+      </c>
+      <c r="D292" s="4">
+        <v>-3.8974880930249499E-2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A293" s="2">
+        <v>0.34498530093003399</v>
+      </c>
+      <c r="B293">
+        <v>5.9868201732548101E-3</v>
+      </c>
+      <c r="C293" s="5">
+        <v>-1.5085899999999999E-2</v>
+      </c>
+      <c r="D293" s="4">
+        <v>-7.2812045109615997E-3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A294" s="2">
+        <v>0.16992820945711501</v>
+      </c>
+      <c r="B294">
+        <v>7.2450922538333296E-2</v>
+      </c>
+      <c r="C294" s="5">
+        <v>0.53037833623667996</v>
+      </c>
+      <c r="D294" s="4">
+        <v>8.16602820262083E-2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A295" s="2">
+        <v>0.28536156743951402</v>
+      </c>
+      <c r="B295">
+        <v>-2.2205910484796001E-2</v>
+      </c>
+      <c r="C295" s="5">
+        <v>0.39985149627434702</v>
+      </c>
+      <c r="D295" s="4">
+        <v>6.7004132914786796E-2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A296" s="2">
+        <v>0.26324966270107902</v>
+      </c>
+      <c r="B296" s="2">
+        <v>0.110122927212173</v>
+      </c>
+      <c r="C296" s="5">
+        <v>0.148480839455742</v>
+      </c>
+      <c r="D296" s="4">
+        <v>-0.116216543787848</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A297" s="2">
+        <v>0.116804380399429</v>
+      </c>
+      <c r="B297" s="2">
+        <v>1.64795846529995E-2</v>
+      </c>
+      <c r="C297" s="5">
+        <v>0.67195174169689698</v>
+      </c>
+      <c r="D297" s="4">
+        <v>6.5379362569156302E-2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A298" s="2">
+        <v>0.38703134872735301</v>
+      </c>
+      <c r="B298" s="2">
+        <v>3.9412675894678402E-2</v>
+      </c>
+      <c r="C298" s="5">
+        <v>0.43359763387366601</v>
+      </c>
+      <c r="D298" s="6">
+        <v>1.9674645241173301E-2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A299" s="2">
+        <v>0.31927530669255599</v>
+      </c>
+      <c r="B299">
+        <v>3.4138317679784001E-2</v>
+      </c>
+      <c r="C299" s="5">
+        <v>1.52289964344828E-2</v>
+      </c>
+      <c r="D299" s="4">
+        <v>-3.77549072511276E-3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A300" s="2">
+        <v>0.32650164369180401</v>
+      </c>
+      <c r="B300">
+        <v>3.9608122684197097E-2</v>
+      </c>
+      <c r="C300" s="5">
+        <v>0.51663891543283302</v>
+      </c>
+      <c r="D300" s="4">
+        <v>6.0309628203999502E-3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A301" s="2">
+        <v>0.20731295601631899</v>
+      </c>
+      <c r="B301">
+        <v>2.4619241633546399E-2</v>
+      </c>
+      <c r="C301" s="5">
+        <v>0.559923398073778</v>
+      </c>
+      <c r="D301" s="4">
+        <v>-1.63204355813805E-2</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A302" s="2">
+        <v>0.67048054871107599</v>
+      </c>
+      <c r="B302" s="2">
+        <v>0.119989587782794</v>
+      </c>
+      <c r="C302" s="5">
+        <v>0.40757400949460099</v>
+      </c>
+      <c r="D302" s="4">
+        <v>-4.9721108074745604E-3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A303" s="2">
+        <v>0.43709874315853597</v>
+      </c>
+      <c r="B303">
+        <v>8.0226124874570402E-4</v>
+      </c>
+      <c r="C303" s="5">
+        <v>0.615415895465936</v>
+      </c>
+      <c r="D303" s="4">
+        <v>-4.7019206955664597E-2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A304" s="2">
+        <v>0.97512767889991303</v>
+      </c>
+      <c r="B304">
+        <v>1.57822202325925E-2</v>
+      </c>
+      <c r="C304" s="5">
+        <v>0.50971659061372898</v>
+      </c>
+      <c r="D304" s="4">
+        <v>-1.8634134823769601E-2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A305" s="2">
+        <v>0.647052289825095</v>
+      </c>
+      <c r="B305">
+        <v>7.5249545639804696E-2</v>
+      </c>
+      <c r="C305" s="5">
+        <v>1.16285936680775</v>
+      </c>
+      <c r="D305" s="4">
+        <v>-8.3409738788836604E-2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A306" s="2">
+        <v>1.0588521723817801</v>
+      </c>
+      <c r="B306">
+        <v>7.9192088242376196E-2</v>
+      </c>
+      <c r="C306" s="5">
+        <v>0.62928160783490805</v>
+      </c>
+      <c r="D306" s="6">
+        <v>2.2954886737962799E-2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A307" s="2">
+        <v>0.73704773470349705</v>
+      </c>
+      <c r="B307" s="2">
+        <v>1.5716958252605901E-2</v>
+      </c>
+      <c r="C307" s="5">
+        <v>0.74279137034089004</v>
+      </c>
+      <c r="D307" s="4">
+        <v>7.1549631380344397E-2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A308" s="2">
+        <v>0.40117529450933798</v>
+      </c>
+      <c r="B308">
+        <v>7.5283244661781996E-3</v>
+      </c>
+      <c r="C308" s="5">
+        <v>0.17390908034903099</v>
+      </c>
+      <c r="D308" s="4">
+        <v>-1.28489820857687E-2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A309" s="2">
+        <v>0.71385796583039896</v>
+      </c>
+      <c r="B309">
+        <v>-7.5091870087534499E-2</v>
+      </c>
+      <c r="C309" s="5">
+        <v>0.51689131653579701</v>
+      </c>
+      <c r="D309" s="4">
+        <v>-5.9058190018812198E-2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A310" s="2">
+        <v>0.759005864394239</v>
+      </c>
+      <c r="B310">
+        <v>4.7699756061418401E-2</v>
+      </c>
+      <c r="C310" s="5">
+        <v>0.78361892817513901</v>
+      </c>
+      <c r="D310" s="4">
+        <v>-2.2566545812179001E-2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A311" s="2">
+        <v>0.563041407313283</v>
+      </c>
+      <c r="B311">
+        <v>4.5668061947868301E-2</v>
+      </c>
+      <c r="C311" s="5">
+        <v>0.57772121971294899</v>
+      </c>
+      <c r="D311" s="6">
+        <v>2.1279394584423902E-2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A312" s="2">
+        <v>0.675763356943339</v>
+      </c>
+      <c r="B312">
+        <v>7.1601551962829593E-2</v>
+      </c>
+      <c r="C312" s="5">
+        <v>0.69461855679113704</v>
+      </c>
+      <c r="D312" s="4">
+        <v>-5.3680236572208797E-3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A313" s="2">
+        <v>1.0542448255642101</v>
+      </c>
+      <c r="B313">
+        <v>6.5459234064324995E-2</v>
+      </c>
+      <c r="C313" s="5">
+        <v>0.395685354157361</v>
+      </c>
+      <c r="D313" s="4">
+        <v>-4.1344869936604097E-3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A314" s="2">
+        <v>0.40145171478740599</v>
+      </c>
+      <c r="B314">
+        <v>-2.5264645912318601E-2</v>
+      </c>
+      <c r="C314" s="5">
+        <v>0.46639129616197</v>
+      </c>
+      <c r="D314" s="4">
+        <v>2.0481847860847301E-4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A315" s="2">
+        <v>0.99565421726606396</v>
+      </c>
+      <c r="B315">
+        <v>-4.3116683495770698E-3</v>
+      </c>
+      <c r="C315" s="5">
+        <v>7.4901430000000005E-2</v>
+      </c>
+      <c r="D315" s="4">
+        <v>-7.4545988222609397E-3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A316" s="2">
+        <v>0.58866869854117698</v>
+      </c>
+      <c r="B316">
+        <v>7.0423478137514095E-2</v>
+      </c>
+      <c r="C316" s="5">
+        <v>1.0524760166671701</v>
+      </c>
+      <c r="D316" s="4">
+        <v>-7.5028659428075295E-2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A317" s="2">
+        <v>0.836621191156533</v>
+      </c>
+      <c r="B317">
+        <v>-9.1815628630511806E-2</v>
+      </c>
+      <c r="C317" s="5">
+        <v>0.41365666117661898</v>
+      </c>
+      <c r="D317" s="4">
+        <v>5.3727514926398497E-2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>0.61090830811149999</v>
+      </c>
+      <c r="B318">
+        <v>-8.4065968178815894E-3</v>
+      </c>
+      <c r="C318" s="5">
+        <v>0.46080358075572803</v>
+      </c>
+      <c r="D318" s="4">
+        <v>-3.0924365212950899E-2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A319" s="2">
+        <v>1.0959597189516901</v>
+      </c>
+      <c r="B319" s="2">
+        <v>0.15159397772409799</v>
+      </c>
+      <c r="C319" s="5">
+        <v>0.39551085890447901</v>
+      </c>
+      <c r="D319" s="4">
+        <v>2.7040426306105099E-2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A320" s="2">
+        <v>0.15763543330503599</v>
+      </c>
+      <c r="B320">
+        <v>-9.2170379873771895E-3</v>
+      </c>
+      <c r="C320" s="5">
+        <v>0.46348969667529</v>
+      </c>
+      <c r="D320" s="4">
+        <v>-2.92473067310118E-2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A321" s="2">
+        <v>0.309906219481836</v>
+      </c>
+      <c r="B321">
+        <v>6.6879488793753605E-2</v>
+      </c>
+      <c r="C321" s="5">
+        <v>0.25292866568285999</v>
+      </c>
+      <c r="D321" s="4">
+        <v>9.595131716363E-3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A322" s="2">
+        <v>0.99423020180621602</v>
+      </c>
+      <c r="B322">
+        <v>4.7246838174879603E-2</v>
+      </c>
+      <c r="C322" s="5">
+        <v>0.55726207439417996</v>
+      </c>
+      <c r="D322" s="4">
+        <v>6.8495369121247304E-2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A323" s="2">
+        <v>0.80762347669934298</v>
+      </c>
+      <c r="B323" s="2">
+        <v>1.42629930696676E-2</v>
+      </c>
+      <c r="C323" s="5">
+        <v>0.82224866250685402</v>
+      </c>
+      <c r="D323" s="6">
+        <v>4.3060530278661399E-2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A324" s="2">
+        <v>0.55610693908726405</v>
+      </c>
+      <c r="B324">
+        <v>-5.7344158817251703E-2</v>
+      </c>
+      <c r="C324" s="5">
+        <v>1.3278494961282199</v>
+      </c>
+      <c r="D324" s="4">
+        <v>2.78345515910495E-2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A325" s="2">
+        <v>0.43670379029895401</v>
+      </c>
+      <c r="B325">
+        <v>-3.2688008522998802E-2</v>
+      </c>
+      <c r="C325" s="5">
+        <v>0.77920009064621298</v>
+      </c>
+      <c r="D325" s="4">
+        <v>-1.09060255272157E-2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A326" s="2">
+        <v>0.69523322605119797</v>
+      </c>
+      <c r="B326" s="2">
+        <v>0.118580973617367</v>
+      </c>
+      <c r="C326" s="5">
+        <v>1.0586387126919501</v>
+      </c>
+      <c r="D326" s="4">
+        <v>8.1181997034294295E-2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A327" s="2">
+        <v>0.47600688660296803</v>
+      </c>
+      <c r="B327">
+        <v>6.6506820272111203E-2</v>
+      </c>
+      <c r="C327" s="5">
+        <v>1.1857354304965899</v>
+      </c>
+      <c r="D327" s="6">
+        <v>3.7625215059570102E-2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A328" s="2">
+        <v>0.19806749350767899</v>
+      </c>
+      <c r="B328">
+        <v>4.8869199330286897E-2</v>
+      </c>
+      <c r="C328" s="5">
+        <v>1.0182041983288499</v>
+      </c>
+      <c r="D328" s="4">
+        <v>3.7707678904223899E-2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A329" s="2">
+        <v>0.80543318834245803</v>
+      </c>
+      <c r="B329">
+        <v>-0.11243977876475</v>
+      </c>
+      <c r="C329" s="5">
+        <v>0.59895063000000004</v>
+      </c>
+      <c r="D329" s="4">
+        <v>-1.97647209831926E-2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>0.36005574812340801</v>
+      </c>
+      <c r="B330">
+        <v>-1.36948814645868E-2</v>
+      </c>
+      <c r="C330" s="5">
+        <v>0.50834858690653795</v>
+      </c>
+      <c r="D330" s="4">
+        <v>-9.2905883797800501E-3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A331" s="2">
+        <v>0.179541154206072</v>
+      </c>
+      <c r="B331" s="2">
+        <v>1.94408964322638E-2</v>
+      </c>
+      <c r="C331" s="5">
+        <v>0.792442072877513</v>
+      </c>
+      <c r="D331" s="4">
+        <v>-5.2159415336658403E-2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A332" s="2">
+        <v>0.167201623868725</v>
+      </c>
+      <c r="B332">
+        <v>-1.3790686560427199E-2</v>
+      </c>
+      <c r="C332" s="5">
+        <v>0.78203836649954195</v>
+      </c>
+      <c r="D332" s="4">
+        <v>-4.2370316115701301E-2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A333" s="2">
+        <v>0.49642611859889901</v>
+      </c>
+      <c r="B333" s="2">
+        <v>0.16905430119251999</v>
+      </c>
+      <c r="C333" s="5">
+        <v>1.1197357863072299</v>
+      </c>
+      <c r="D333" s="4">
+        <v>-5.7369947235350001E-2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A334" s="2">
+        <v>0.34993372267741801</v>
+      </c>
+      <c r="B334" s="2">
+        <v>1.1354804455779299E-2</v>
+      </c>
+      <c r="C334" s="5">
+        <v>0.71332830000000003</v>
+      </c>
+      <c r="D334" s="4">
+        <v>2.58009844922681E-2</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A335" s="2">
+        <v>0.21321900596833801</v>
+      </c>
+      <c r="B335">
+        <v>6.4143683786873296E-2</v>
+      </c>
+      <c r="C335" s="5">
+        <v>0.40855433966749499</v>
+      </c>
+      <c r="D335" s="4">
+        <v>3.8015280619254001E-2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A336" s="2">
+        <v>0.37574499789334997</v>
+      </c>
+      <c r="B336">
+        <v>7.8229261907338907E-2</v>
+      </c>
+      <c r="C336" s="5">
+        <v>0.99010123698416397</v>
+      </c>
+      <c r="D336" s="4">
+        <v>-1.7867513753892401E-2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A337" s="2">
+        <v>0.31089749891861601</v>
+      </c>
+      <c r="B337">
+        <v>8.1056099303422904E-2</v>
+      </c>
+      <c r="C337" s="5">
+        <v>1.2732352418480899</v>
+      </c>
+      <c r="D337" s="4">
+        <v>-6.8502805250008306E-2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A338" s="2">
+        <v>0.28381675215140401</v>
+      </c>
+      <c r="B338" s="2">
+        <v>2.3637922889830101E-2</v>
+      </c>
+      <c r="C338" s="5">
+        <v>0.67156260206878304</v>
+      </c>
+      <c r="D338" s="4">
+        <v>5.8739821190455198E-2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A339" s="2">
+        <v>0.33127787800861702</v>
+      </c>
+      <c r="B339">
+        <v>6.4714414775522297E-2</v>
+      </c>
+      <c r="C339" s="5">
+        <v>0.44283667755647199</v>
+      </c>
+      <c r="D339" s="4">
+        <v>-0.10075978571967401</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A340" s="2">
+        <v>0.27124065402115799</v>
+      </c>
+      <c r="B340" s="2">
+        <v>2.0322481408463201E-2</v>
+      </c>
+      <c r="C340" s="5">
+        <v>0.10529953590964899</v>
+      </c>
+      <c r="D340" s="4">
+        <v>-9.6427338662746394E-3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A341" s="2">
+        <v>0.27293900744239902</v>
+      </c>
+      <c r="B341" s="2">
+        <v>2.7267012177678601E-2</v>
+      </c>
+      <c r="C341" s="5">
+        <v>0.76120130144570797</v>
+      </c>
+      <c r="D341" s="6">
+        <v>2.7777430255890499E-2</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A342" s="2">
+        <v>0.47882232187774199</v>
+      </c>
+      <c r="B342">
+        <v>-4.2409393746495903E-2</v>
+      </c>
+      <c r="C342" s="5">
+        <v>0.75043461496089703</v>
+      </c>
+      <c r="D342" s="4">
+        <v>-7.8823649192858794E-2</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A343" s="2">
+        <v>0.474575127116726</v>
+      </c>
+      <c r="B343">
+        <v>-7.7553679815889898E-3</v>
+      </c>
+      <c r="C343" s="5">
+        <v>0.64790670230909297</v>
+      </c>
+      <c r="D343" s="4">
+        <v>-6.0047169183210299E-2</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A344" s="2">
+        <v>0.47247578402596901</v>
+      </c>
+      <c r="B344" s="2">
+        <v>0.12936421793522901</v>
+      </c>
+      <c r="C344" s="5">
+        <v>0.366441153949917</v>
+      </c>
+      <c r="D344" s="4">
+        <v>7.1754572145226597E-2</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A345" s="2">
+        <v>0.358049964311702</v>
+      </c>
+      <c r="B345">
+        <v>-1.39018075088578E-2</v>
+      </c>
+      <c r="C345" s="5">
+        <v>0.62174114545804204</v>
+      </c>
+      <c r="D345" s="4">
+        <v>-5.4206445333948904E-3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A346" s="2">
+        <v>0.388380648040132</v>
+      </c>
+      <c r="B346">
+        <v>-7.2348808850113003E-3</v>
+      </c>
+      <c r="C346" s="5">
+        <v>1.0872061401758999</v>
+      </c>
+      <c r="D346" s="4">
+        <v>6.3986047641426305E-2</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A347" s="2">
+        <v>0.46460891900915302</v>
+      </c>
+      <c r="B347">
+        <v>1.5778866978678401E-2</v>
+      </c>
+      <c r="C347" s="5">
+        <v>0.46867498708371602</v>
+      </c>
+      <c r="D347" s="4">
+        <v>8.6604861125092095E-2</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A348" s="2">
+        <v>0.53284300378987803</v>
+      </c>
+      <c r="B348">
+        <v>-6.9856432151383402E-2</v>
+      </c>
+      <c r="C348" s="5">
+        <v>0.88140700204829703</v>
+      </c>
+      <c r="D348" s="4">
+        <v>2.9477202284700701E-2</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A349" s="2">
+        <v>0.165412303394948</v>
+      </c>
+      <c r="B349">
+        <v>3.0046536604390099E-2</v>
+      </c>
+      <c r="C349" s="5">
+        <v>-1.69733E-2</v>
+      </c>
+      <c r="D349" s="6">
+        <v>1.48564651402664E-2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A350" s="2">
+        <v>0.34795113483878198</v>
+      </c>
+      <c r="B350">
+        <v>-2.7070654915866202E-3</v>
+      </c>
+      <c r="C350" s="5">
+        <v>4.2455079999999999E-2</v>
+      </c>
+      <c r="D350" s="4">
+        <v>3.7077115317510199E-2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A351" s="2">
+        <v>0.27020714781474298</v>
+      </c>
+      <c r="B351">
+        <v>4.4334824751551096E-3</v>
+      </c>
+      <c r="C351" s="5">
+        <v>0.298359968722407</v>
+      </c>
+      <c r="D351" s="4">
+        <v>-1.5826711882001899E-2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A352" s="2">
+        <v>0.43070086157424498</v>
+      </c>
+      <c r="B352" s="2">
+        <v>2.8771347380228601E-2</v>
+      </c>
+      <c r="C352" s="5">
+        <v>0.30993360253395702</v>
+      </c>
+      <c r="D352" s="4">
+        <v>-2.3972389880791499E-2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A353" s="2">
+        <v>0.20658165266946099</v>
+      </c>
+      <c r="B353">
+        <v>-1.49971356949126E-2</v>
+      </c>
+      <c r="C353" s="5">
+        <v>0.145133293476467</v>
+      </c>
+      <c r="D353" s="4">
+        <v>-4.6397824779201902E-2</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A354" s="2">
+        <v>0.495658489014765</v>
+      </c>
+      <c r="B354">
+        <v>-4.6680854816083701E-3</v>
+      </c>
+      <c r="C354" s="5">
+        <v>8.1723530000000003E-2</v>
+      </c>
+      <c r="D354" s="6">
+        <v>5.2415554221162203E-2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A355" s="2">
+        <v>0.23943019233194199</v>
+      </c>
+      <c r="B355" s="2">
+        <v>4.4951402610734999E-2</v>
+      </c>
+      <c r="C355" s="5">
+        <v>0.55352739480916802</v>
+      </c>
+      <c r="D355" s="4">
+        <v>-8.0394404844185793E-2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>0.26414035913381201</v>
+      </c>
+      <c r="B356">
+        <v>6.5263702660382103E-2</v>
+      </c>
+      <c r="C356" s="5">
+        <v>0.58878586609926298</v>
+      </c>
+      <c r="D356" s="4">
+        <v>-2.8622287404299E-2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A357" s="2">
+        <v>0.36636764889083501</v>
+      </c>
+      <c r="B357">
+        <v>2.8603541921722801E-3</v>
+      </c>
+      <c r="C357" s="5">
+        <v>0.57474866000000002</v>
+      </c>
+      <c r="D357" s="4">
+        <v>7.0502169151205302E-2</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A358" s="2">
+        <v>0.15984358501816501</v>
+      </c>
+      <c r="B358">
+        <v>2.7361168369553601E-2</v>
+      </c>
+      <c r="C358" s="5">
+        <v>0.43678412268212102</v>
+      </c>
+      <c r="D358" s="4">
+        <v>-6.0081770089463603E-2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>7.2143827777295194E-2</v>
+      </c>
+      <c r="B359">
+        <v>-1.0840487443189399E-2</v>
+      </c>
+      <c r="C359" s="5">
+        <v>0.25946488912962501</v>
+      </c>
+      <c r="D359" s="4">
+        <v>-3.4648616108670399E-2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A360" s="2">
+        <v>0.407188692303175</v>
+      </c>
+      <c r="B360" s="2">
+        <v>1.76558991433787E-2</v>
+      </c>
+      <c r="C360" s="5">
+        <v>5.6096689999999998E-2</v>
+      </c>
+      <c r="D360" s="6">
+        <v>6.1583974131563503E-2</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A361" s="2">
+        <v>0.83197800787276299</v>
+      </c>
+      <c r="B361">
+        <v>-3.1849141706018401E-2</v>
+      </c>
+      <c r="C361" s="5">
+        <v>0.38557501021338197</v>
+      </c>
+      <c r="D361" s="6">
+        <v>1.8638545735599501E-2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A362" s="2">
+        <v>0.55978595190507596</v>
+      </c>
+      <c r="B362">
+        <v>-1.3225768546020001E-2</v>
+      </c>
+      <c r="C362" s="5">
+        <v>0.44774457551406999</v>
+      </c>
+      <c r="D362" s="4">
+        <v>1.3013705826784201E-3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>0.95974428808429801</v>
+      </c>
+      <c r="B363">
+        <v>-9.5384798153752295E-2</v>
+      </c>
+      <c r="C363" s="5">
+        <v>0.45101893365191797</v>
+      </c>
+      <c r="D363" s="4">
+        <v>-9.09142044154416E-3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A364" s="2">
+        <v>0.52098963403095999</v>
+      </c>
+      <c r="B364" s="2">
+        <v>0.102879004020225</v>
+      </c>
+      <c r="C364" s="5">
+        <v>0.65058829926414297</v>
+      </c>
+      <c r="D364" s="6">
+        <v>2.4470542309466901E-2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A365" s="2">
+        <v>0.55662041066456203</v>
+      </c>
+      <c r="B365">
+        <v>3.7277258425937299E-3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>0.70859454863106297</v>
+      </c>
+      <c r="B366">
+        <v>-2.4610803303353499E-2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A367" s="2">
+        <v>0.68720648667876605</v>
+      </c>
+      <c r="B367" s="2">
+        <v>2.12425521267561E-2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A368" s="2">
+        <v>0.54521968460676795</v>
+      </c>
+      <c r="B368">
+        <v>-1.70481649690215E-2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" s="2">
+        <v>0.406885292878579</v>
+      </c>
+      <c r="B369">
+        <v>-2.9816674985061398E-2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" s="2">
+        <v>0.72457354775275395</v>
+      </c>
+      <c r="B370">
+        <v>-2.7866033846659099E-2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" s="2">
+        <v>0.66858891810406396</v>
+      </c>
+      <c r="B371">
+        <v>9.0541257042652007E-2</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" s="2">
+        <v>0.68551751710379905</v>
+      </c>
+      <c r="B372">
+        <v>-2.5062601659178601E-2</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373" s="2">
+        <v>0.58393904102789795</v>
+      </c>
+      <c r="B373">
+        <v>-2.8932061142587399E-2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" s="2">
+        <v>0.47117125007382998</v>
+      </c>
+      <c r="B374">
+        <v>-3.4890595323649597E-2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" s="2">
+        <v>0.54406700465036695</v>
+      </c>
+      <c r="B375">
+        <v>2.8869023526328301E-2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" s="2">
+        <v>0.42569572009552697</v>
+      </c>
+      <c r="B376">
+        <v>-2.9086999088970202E-2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" s="2">
+        <v>1.02906291725784</v>
+      </c>
+      <c r="B377">
+        <v>1.45907006109644E-3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" s="2">
+        <v>0.65786794247392499</v>
+      </c>
+      <c r="B378">
+        <v>-5.9990000258408598E-3</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" s="2">
+        <v>0.624836372861584</v>
+      </c>
+      <c r="B379" s="2">
+        <v>0.11883001388830999</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" s="2">
+        <v>0.53311622473462394</v>
+      </c>
+      <c r="B380">
+        <v>9.5326251913662896E-2</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" s="2">
+        <v>0.85639785753939901</v>
+      </c>
+      <c r="B381" s="2">
+        <v>0.136860899553439</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>0.484044423491031</v>
+      </c>
+      <c r="B382">
+        <v>-8.8321717532067693E-3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" s="2">
+        <v>0.968198447388816</v>
+      </c>
+      <c r="B383">
+        <v>-0.136393222473113</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" s="2">
+        <v>0.56680988803537802</v>
+      </c>
+      <c r="B384">
+        <v>3.9878973963596697E-3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" s="2">
+        <v>0.53383027184182397</v>
+      </c>
+      <c r="B385">
+        <v>3.27401215587385E-3</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" s="2">
+        <v>0.62281576397132499</v>
+      </c>
+      <c r="B386" s="2">
+        <v>5.6215396465796201E-2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" s="2">
+        <v>0.48597378948866299</v>
+      </c>
+      <c r="B387">
+        <v>-4.5061466398101102E-2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" s="2">
+        <v>0.44709927787824599</v>
+      </c>
+      <c r="B388">
+        <v>7.83073520459793E-2</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>0.51468293030504297</v>
+      </c>
+      <c r="B389">
+        <v>-4.2137190535379697E-2</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" s="2">
+        <v>0.50090990773371402</v>
+      </c>
+      <c r="B390">
+        <v>-2.8692079964091701E-2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" s="2">
+        <v>0.704408949064803</v>
+      </c>
+      <c r="B391" s="2">
+        <v>1.53138463467524E-2</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" s="2">
+        <v>0.172557761980727</v>
+      </c>
+      <c r="B392">
+        <v>3.6467314540222198E-3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" s="2">
+        <v>0.52487091900564298</v>
+      </c>
+      <c r="B393">
+        <v>-1.60817654330539E-2</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" s="2">
+        <v>0.175648333164936</v>
+      </c>
+      <c r="B394">
+        <v>-6.7796123316452399E-3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>0.52739143879331796</v>
+      </c>
+      <c r="B395" s="2">
+        <v>0.165861969328122</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396" s="2">
+        <v>0.38409756385577298</v>
+      </c>
+      <c r="B396">
+        <v>-0.13085078081124099</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397" s="2">
+        <v>0.214193101961135</v>
+      </c>
+      <c r="B397">
+        <v>-1.8787008389651099E-3</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398" s="2">
+        <v>0.49401207920022799</v>
+      </c>
+      <c r="B398">
+        <v>-5.4951649518123397E-2</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>7.6508435209019204E-2</v>
+      </c>
+      <c r="B399">
+        <v>7.1442910207462603E-3</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400" s="2">
+        <v>0.638018287236364</v>
+      </c>
+      <c r="B400" s="2">
+        <v>0.126285973062298</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401" s="2">
+        <v>0.33884999535374399</v>
+      </c>
+      <c r="B401">
+        <v>-7.1765294709764699E-2</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402" s="2">
+        <v>0.42369546090043603</v>
+      </c>
+      <c r="B402">
+        <v>-9.1214227452478994E-2</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" s="2">
+        <v>0.247988444566941</v>
+      </c>
+      <c r="B403">
+        <v>-7.9260248494933294E-2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404" s="2">
+        <v>0.35737911036758102</v>
+      </c>
+      <c r="B404">
+        <v>4.0168332697684099E-2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405" s="2">
+        <v>0.12351102757136601</v>
+      </c>
+      <c r="B405">
+        <v>-1.97591226896691E-2</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406" s="2">
+        <v>0.46193159711039</v>
+      </c>
+      <c r="B406" s="2">
+        <v>3.8272335837694099E-2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407" s="2">
+        <v>0.23376052943369499</v>
+      </c>
+      <c r="B407">
+        <v>2.6025691039257601E-2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408" s="2">
+        <v>0.266403019379434</v>
+      </c>
+      <c r="B408">
+        <v>-6.8632153641040694E-2</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>9.6919827205124598E-2</v>
+      </c>
+      <c r="B409">
+        <v>-5.5482003471002397E-3</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410" s="2">
+        <v>0.24946257943425401</v>
+      </c>
+      <c r="B410" s="2">
+        <v>1.2097258328177599E-2</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411" s="2">
+        <v>0.23556672026717501</v>
+      </c>
+      <c r="B411">
+        <v>-1.46785387033495E-2</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412" s="2">
+        <v>0.64011970893666403</v>
+      </c>
+      <c r="B412">
+        <v>-6.6043105826724097E-2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413" s="2">
+        <v>0.52163081529201505</v>
+      </c>
+      <c r="B413" s="2">
+        <v>0.154455982912586</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414" s="2">
+        <v>0.220005865989543</v>
+      </c>
+      <c r="B414">
+        <v>-6.0282338373652801E-2</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415" s="2">
+        <v>0.43225622695721799</v>
+      </c>
+      <c r="B415">
+        <v>4.4225577911476098E-2</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416" s="2">
+        <v>0.25991721018181202</v>
+      </c>
+      <c r="B416">
+        <v>-4.5700105327887E-2</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417" s="2">
+        <v>0.83548162860699804</v>
+      </c>
+      <c r="B417">
+        <v>-7.9334698173451096E-2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418" s="2">
+        <v>0.452796907596203</v>
+      </c>
+      <c r="B418">
+        <v>-1.85826072321645E-2</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419" s="2">
+        <v>0.42728885015212398</v>
+      </c>
+      <c r="B419">
+        <v>7.2977577382020001E-2</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420" s="2">
+        <v>0.66028857839106503</v>
+      </c>
+      <c r="B420">
+        <v>-5.85783110838233E-3</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421" s="2">
+        <v>0.29684375226923598</v>
+      </c>
+      <c r="B421">
+        <v>-6.1870082585623799E-2</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422" s="2">
+        <v>0.51134445823966801</v>
+      </c>
+      <c r="B422" s="2">
+        <v>1.48506248552097E-2</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423" s="2">
+        <v>0.56287005124836398</v>
+      </c>
+      <c r="B423" s="2">
+        <v>2.5608705122918601E-2</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424" s="2">
+        <v>0.49985086838284598</v>
+      </c>
+      <c r="B424">
+        <v>-3.4835422224754997E-2</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" s="2">
+        <v>0.23466488747421199</v>
+      </c>
+      <c r="B425">
+        <v>-8.8056430686152806E-2</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426" s="2">
+        <v>0.44603876020290001</v>
+      </c>
+      <c r="B426">
+        <v>-1.4250846366679599E-2</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427" s="2">
+        <v>0.25842923753595298</v>
+      </c>
+      <c r="B427">
+        <v>3.5972947578432397E-2</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428" s="2">
+        <v>0.389221328878118</v>
+      </c>
+      <c r="B428">
+        <v>3.3305290759895502E-2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429" s="2">
+        <v>0.29842797849754299</v>
+      </c>
+      <c r="B429">
+        <v>-2.9887123814701998E-2</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430" s="2">
+        <v>0.20450479815405201</v>
+      </c>
+      <c r="B430" s="2">
+        <v>2.2576373236405101E-2</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431">
+        <v>-6.7638334294159705E-2</v>
+      </c>
+      <c r="B431">
+        <v>-7.8881803473594303E-2</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432" s="2">
+        <v>0.176797209618585</v>
+      </c>
+      <c r="B432">
+        <v>-1.7778171502627501E-2</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433">
+        <v>8.5491301586965399E-2</v>
+      </c>
+      <c r="B433">
+        <v>3.4089748602746599E-2</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434">
+        <v>8.4962206403378496E-2</v>
+      </c>
+      <c r="B434">
+        <v>-3.09564958807226E-2</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435" s="2">
+        <v>0.70717270802461096</v>
+      </c>
+      <c r="B435">
+        <v>-6.5286003344902602E-2</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436" s="2">
+        <v>0.50408217485627105</v>
+      </c>
+      <c r="B436" s="2">
+        <v>0.115920411374819</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437">
+        <v>0.73105281031657099</v>
+      </c>
+      <c r="B437">
+        <v>-6.36397114672341E-2</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438" s="2">
+        <v>0.64456514938717502</v>
+      </c>
+      <c r="B438">
+        <v>9.2383918253294797E-2</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439" s="2">
+        <v>0.69981211057762305</v>
+      </c>
+      <c r="B439" s="2">
+        <v>0.132330627133073</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440" s="2">
+        <v>0.102421722874094</v>
+      </c>
+      <c r="B440">
+        <v>-1.2719411675988499E-2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441" s="2">
+        <v>0.23652634728438601</v>
+      </c>
+      <c r="B441">
+        <v>-3.9945323806031899E-2</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442" s="2">
+        <v>0.25412470265074599</v>
+      </c>
+      <c r="B442">
+        <v>3.1887097079164303E-2</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443" s="2">
+        <v>1.1263418373306799</v>
+      </c>
+      <c r="B443" s="2">
+        <v>1.8712085099272299E-2</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444" s="2">
+        <v>0.245297173083839</v>
+      </c>
+      <c r="B444">
+        <v>-1.69620195077652E-2</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445" s="2">
+        <v>0.80285798903722405</v>
+      </c>
+      <c r="B445">
+        <v>-7.1992252725849901E-2</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446" s="2">
+        <v>0.32923348039154898</v>
+      </c>
+      <c r="B446">
+        <v>7.3922225792983895E-2</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447" s="2">
+        <v>0.38523850853911501</v>
+      </c>
+      <c r="B447">
+        <v>-3.8729718879765597E-2</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448" s="2">
+        <v>0.23342038089941</v>
+      </c>
+      <c r="B448">
+        <v>1.0765329444672399E-3</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449" s="2">
+        <v>0.81843370675396099</v>
+      </c>
+      <c r="B449" s="2">
+        <v>1.5840781027521299E-2</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450" s="2">
+        <v>0.39808450572322002</v>
+      </c>
+      <c r="B450">
+        <v>-5.1251273594854797E-2</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451" s="2">
+        <v>1.2374281073134501</v>
+      </c>
+      <c r="B451" s="2">
+        <v>3.05674090952931E-2</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452" s="2">
+        <v>0.80385716589987199</v>
+      </c>
+      <c r="B452" s="2">
+        <v>4.2308022547844902E-2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453" s="2">
+        <v>0.79681268544811401</v>
+      </c>
+      <c r="B453">
+        <v>-2.8806381251936599E-2</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454">
+        <v>0.54321918382425005</v>
+      </c>
+      <c r="B454">
+        <v>-2.9062184956389101E-2</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455" s="2">
+        <v>0.27584833609748599</v>
+      </c>
+      <c r="B455">
+        <v>5.2491884201035198E-2</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456" s="2">
+        <v>0.88021422292834595</v>
+      </c>
+      <c r="B456">
+        <v>-4.8095247833876899E-2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457" s="2">
+        <v>0.39680078592193202</v>
+      </c>
+      <c r="B457">
+        <v>-2.25343451711283E-2</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458" s="2">
+        <v>0.25037173875968899</v>
+      </c>
+      <c r="B458">
+        <v>-5.4484220461510302E-2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459">
+        <v>0.45137618807139002</v>
+      </c>
+      <c r="B459">
+        <v>6.3613313236967799E-3</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460" s="2">
+        <v>0.692143835807841</v>
+      </c>
+      <c r="B460">
+        <v>-3.3299192505852802E-2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461" s="2">
+        <v>1.14129553411415</v>
+      </c>
+      <c r="B461" s="2">
+        <v>0.100256004099134</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" s="2">
+        <v>0.56717590832572795</v>
+      </c>
+      <c r="B462">
+        <v>-9.8114817413369002E-3</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" s="2">
+        <v>0.65504762046318599</v>
+      </c>
+      <c r="B463">
+        <v>-4.6556056352293297E-2</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464" s="2">
+        <v>1.08215392519153</v>
+      </c>
+      <c r="B464" s="2">
+        <v>0.18850558298857401</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465" s="2">
+        <v>0.97111591086205395</v>
+      </c>
+      <c r="B465">
+        <v>-7.3194011395848205E-2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466" s="2">
+        <v>0.46739736572490498</v>
+      </c>
+      <c r="B466">
+        <v>-2.20684045885081E-2</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467">
+        <v>0.74461851207637997</v>
+      </c>
+      <c r="B467">
+        <v>3.8850700221958703E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E5C69C2-CBD3-D144-AA1F-12ADE0CF310B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853D1457-A6CA-5742-971E-5425FEE7F6BD}">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>-0.20111499999999999</v>
+      </c>
+      <c r="B3">
+        <v>-0.16394400000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>-4.2373000000000001E-2</v>
+      </c>
+      <c r="B4">
+        <v>-0.250388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>-0.390764</v>
+      </c>
+      <c r="B5">
+        <v>-0.25168499999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>-4.5267000000000002E-2</v>
+      </c>
+      <c r="B6">
+        <v>-0.195462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>-0.188473</v>
+      </c>
+      <c r="B7">
+        <v>-0.16442100000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>-0.33157500000000001</v>
+      </c>
+      <c r="B8">
+        <v>-0.31601800000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>-4.9544999999999999E-2</v>
+      </c>
+      <c r="B9">
+        <v>-0.25057200000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>-1.9726E-2</v>
+      </c>
+      <c r="B10">
+        <v>-0.18127499999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>6.6270999999999997E-2</v>
+      </c>
+      <c r="B11">
+        <v>-0.21399199999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>-6.8983000000000003E-2</v>
+      </c>
+      <c r="B12">
+        <v>-4.0472000000000001E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>-0.32103799999999999</v>
+      </c>
+      <c r="B13">
+        <v>-0.24132400000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>-0.28515699999999999</v>
+      </c>
+      <c r="B14">
+        <v>-0.19600100000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>-0.181619</v>
+      </c>
+      <c r="B15">
+        <v>-0.27379399999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>-9.2121999999999996E-2</v>
+      </c>
+      <c r="B16">
+        <v>-0.35525400000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>-0.13888200000000001</v>
+      </c>
+      <c r="B17">
+        <v>-9.4816999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>-0.23303499999999999</v>
+      </c>
+      <c r="B18">
+        <v>-0.226081</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>-5.2941000000000002E-2</v>
+      </c>
+      <c r="B19">
+        <v>-0.17033000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>-0.108489</v>
+      </c>
+      <c r="B20">
+        <v>-0.304317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>-3.4597999999999997E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>-0.27767700000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>-0.1908</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>